--- a/config/Excel/Talents.xlsx
+++ b/config/Excel/Talents.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{952A56C6-63FC-41E5-86F7-833270B9349C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C41F0896-49EA-4479-9BD4-CD174380C9A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Talents" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="337">
   <si>
     <t>類型</t>
   </si>
@@ -38,18 +51,6 @@
   </si>
   <si>
     <t>屬性桶</t>
-  </si>
-  <si>
-    <t>低階值</t>
-  </si>
-  <si>
-    <t>高階值</t>
-  </si>
-  <si>
-    <t>每級值</t>
-  </si>
-  <si>
-    <t>解鎖數</t>
   </si>
   <si>
     <t>停用</t>
@@ -1032,6 +1033,20 @@
   <si>
     <t>體質總值額外提高</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>每級增加值</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>威脅值</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>TRUE</t>
+  </si>
+  <si>
+    <t>潛力已無解鎖限制，改用威能點，此舊解鎖威能停用</t>
   </si>
 </sst>
 </file>
@@ -1624,12 +1639,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -2006,10 +2024,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M89"/>
+  <dimension ref="A1:K89"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="7" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.625" style="2" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2029,2589 +2051,2595 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
+        <v>333</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G2">
         <v>0.5</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="M2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H2" s="2">
+        <v>2</v>
+      </c>
+      <c r="K2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G3">
         <v>0.5</v>
       </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="M3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H3" s="2">
+        <v>2</v>
+      </c>
+      <c r="K3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G4">
         <v>0.5</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="M4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H4" s="2">
+        <v>2</v>
+      </c>
+      <c r="K4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G5">
         <v>0.5</v>
       </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H5" s="2">
+        <v>2</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G6">
         <v>0.5</v>
       </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="M6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H6" s="2">
+        <v>2</v>
+      </c>
+      <c r="K6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G7">
         <v>0.5</v>
       </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="M7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H7" s="2">
+        <v>2</v>
+      </c>
+      <c r="K7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E8" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G8">
         <v>0.5</v>
       </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="M8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H8" s="2">
+        <v>2</v>
+      </c>
+      <c r="K8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F9" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G9">
         <v>0.5</v>
       </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="M9" t="s">
+      <c r="H9" s="2">
+        <v>2</v>
+      </c>
+      <c r="K9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10">
-        <v>2</v>
-      </c>
-      <c r="C10" t="s">
-        <v>53</v>
-      </c>
-      <c r="D10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E10" t="s">
-        <v>55</v>
-      </c>
-      <c r="F10" t="s">
-        <v>56</v>
       </c>
       <c r="G10">
         <v>5</v>
       </c>
-      <c r="H10">
-        <v>10</v>
-      </c>
-      <c r="M10" t="s">
+      <c r="H10" s="2">
+        <v>2</v>
+      </c>
+      <c r="K10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11">
-        <v>2</v>
-      </c>
-      <c r="C11" t="s">
-        <v>58</v>
-      </c>
-      <c r="D11" t="s">
-        <v>59</v>
-      </c>
-      <c r="E11" t="s">
-        <v>60</v>
-      </c>
-      <c r="F11" t="s">
-        <v>61</v>
       </c>
       <c r="G11">
         <v>75</v>
       </c>
-      <c r="H11">
-        <v>150</v>
-      </c>
-      <c r="M11" t="s">
+      <c r="H11" s="2">
+        <v>2</v>
+      </c>
+      <c r="K11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" t="s">
         <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12">
-        <v>2</v>
-      </c>
-      <c r="C12" t="s">
-        <v>63</v>
-      </c>
-      <c r="D12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E12" t="s">
-        <v>65</v>
-      </c>
-      <c r="F12" t="s">
-        <v>66</v>
       </c>
       <c r="G12">
         <v>5</v>
       </c>
-      <c r="H12">
-        <v>10</v>
-      </c>
-      <c r="M12" t="s">
+      <c r="H12" s="2">
+        <v>2</v>
+      </c>
+      <c r="K12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13" t="s">
         <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13">
-        <v>2</v>
-      </c>
-      <c r="C13" t="s">
-        <v>68</v>
-      </c>
-      <c r="D13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E13" t="s">
-        <v>70</v>
-      </c>
-      <c r="F13" t="s">
-        <v>71</v>
       </c>
       <c r="G13">
         <v>5</v>
       </c>
-      <c r="H13">
-        <v>10</v>
-      </c>
-      <c r="M13" t="s">
+      <c r="H13" s="2">
+        <v>2</v>
+      </c>
+      <c r="K13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" t="s">
         <v>72</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14">
-        <v>2</v>
-      </c>
-      <c r="C14" t="s">
-        <v>73</v>
-      </c>
-      <c r="D14" t="s">
-        <v>74</v>
-      </c>
-      <c r="E14" t="s">
-        <v>75</v>
-      </c>
-      <c r="F14" t="s">
-        <v>76</v>
       </c>
       <c r="G14">
         <v>1</v>
       </c>
-      <c r="H14">
-        <v>2</v>
-      </c>
-      <c r="M14" t="s">
+      <c r="H14" s="2">
+        <v>2</v>
+      </c>
+      <c r="K14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" t="s">
         <v>77</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15">
-        <v>2</v>
-      </c>
-      <c r="C15" t="s">
-        <v>78</v>
-      </c>
-      <c r="D15" t="s">
-        <v>79</v>
-      </c>
-      <c r="E15" t="s">
-        <v>80</v>
-      </c>
-      <c r="F15" t="s">
-        <v>81</v>
       </c>
       <c r="G15">
         <v>1</v>
       </c>
-      <c r="H15">
-        <v>2</v>
-      </c>
-      <c r="M15" t="s">
+      <c r="H15" s="2">
+        <v>2</v>
+      </c>
+      <c r="K15" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+      <c r="C16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" t="s">
+        <v>80</v>
+      </c>
+      <c r="E16" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" t="s">
         <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16">
-        <v>2</v>
-      </c>
-      <c r="C16" t="s">
-        <v>83</v>
-      </c>
-      <c r="D16" t="s">
-        <v>84</v>
-      </c>
-      <c r="E16" t="s">
-        <v>85</v>
-      </c>
-      <c r="F16" t="s">
-        <v>86</v>
       </c>
       <c r="G16">
         <v>1</v>
       </c>
-      <c r="H16">
-        <v>2</v>
-      </c>
-      <c r="M16" t="s">
+      <c r="H16" s="2">
+        <v>2</v>
+      </c>
+      <c r="K16" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17" t="s">
+        <v>84</v>
+      </c>
+      <c r="D17" t="s">
+        <v>85</v>
+      </c>
+      <c r="E17" t="s">
+        <v>86</v>
+      </c>
+      <c r="F17" t="s">
         <v>87</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17">
-        <v>2</v>
-      </c>
-      <c r="C17" t="s">
-        <v>88</v>
-      </c>
-      <c r="D17" t="s">
-        <v>89</v>
-      </c>
-      <c r="E17" t="s">
-        <v>90</v>
-      </c>
-      <c r="F17" t="s">
-        <v>91</v>
       </c>
       <c r="G17">
         <v>1</v>
       </c>
-      <c r="H17">
-        <v>2</v>
-      </c>
-      <c r="M17" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H17" s="2">
+        <v>2</v>
+      </c>
+      <c r="K17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B18">
         <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D18" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E18" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F18" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G18">
         <v>0.5</v>
       </c>
-      <c r="H18">
-        <v>1</v>
-      </c>
-      <c r="M18" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H18" s="2">
+        <v>2</v>
+      </c>
+      <c r="K18" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B19">
         <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D19" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E19" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F19" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G19">
         <v>0.5</v>
       </c>
-      <c r="H19">
-        <v>1</v>
-      </c>
-      <c r="M19" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H19" s="2">
+        <v>2</v>
+      </c>
+      <c r="K19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B20">
         <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D20" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E20" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F20" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G20">
         <v>1</v>
       </c>
-      <c r="H20">
-        <v>2</v>
-      </c>
-      <c r="M20" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H20" s="2">
+        <v>2</v>
+      </c>
+      <c r="K20" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B21">
         <v>3</v>
       </c>
       <c r="C21" t="s">
+        <v>104</v>
+      </c>
+      <c r="D21" t="s">
+        <v>105</v>
+      </c>
+      <c r="E21" t="s">
+        <v>106</v>
+      </c>
+      <c r="F21" t="s">
+        <v>107</v>
+      </c>
+      <c r="G21">
+        <v>2</v>
+      </c>
+      <c r="H21" s="2">
+        <v>2</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="K21" t="s">
         <v>108</v>
       </c>
-      <c r="D21" t="s">
-        <v>109</v>
-      </c>
-      <c r="E21" t="s">
-        <v>110</v>
-      </c>
-      <c r="F21" t="s">
-        <v>111</v>
-      </c>
-      <c r="G21">
-        <v>2</v>
-      </c>
-      <c r="H21">
-        <v>4</v>
-      </c>
-      <c r="J21">
-        <v>3</v>
-      </c>
-      <c r="M21" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B22">
         <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D22" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E22" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F22" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G22">
         <v>0.5</v>
       </c>
-      <c r="H22">
-        <v>1</v>
-      </c>
-      <c r="M22" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H22" s="2">
+        <v>2</v>
+      </c>
+      <c r="K22" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B23">
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D23" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E23" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F23" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G23">
         <v>0.5</v>
       </c>
-      <c r="H23">
-        <v>1</v>
-      </c>
-      <c r="M23" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H23" s="2">
+        <v>2</v>
+      </c>
+      <c r="K23" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B24">
         <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D24" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E24" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F24" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G24">
         <v>0.5</v>
       </c>
-      <c r="H24">
-        <v>1</v>
-      </c>
-      <c r="M24" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H24" s="2">
+        <v>2</v>
+      </c>
+      <c r="K24" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B25">
         <v>3</v>
       </c>
       <c r="C25" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D25" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E25" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F25" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G25">
         <v>0.5</v>
       </c>
-      <c r="H25">
-        <v>1</v>
-      </c>
-      <c r="M25" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H25" s="2">
+        <v>2</v>
+      </c>
+      <c r="K25" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B26">
         <v>4</v>
       </c>
       <c r="C26" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D26" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E26" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F26" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G26">
         <v>0.5</v>
       </c>
-      <c r="H26">
-        <v>1</v>
-      </c>
-      <c r="M26" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H26" s="2">
+        <v>2</v>
+      </c>
+      <c r="K26" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B27">
         <v>4</v>
       </c>
       <c r="C27" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D27" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E27" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F27" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="G27">
         <v>0.5</v>
       </c>
-      <c r="H27">
-        <v>1</v>
-      </c>
-      <c r="M27" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H27" s="2">
+        <v>2</v>
+      </c>
+      <c r="K27" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B28">
         <v>4</v>
       </c>
       <c r="C28" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D28" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E28" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F28" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="G28">
         <v>0.5</v>
       </c>
-      <c r="H28">
-        <v>1</v>
-      </c>
-      <c r="M28" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H28" s="2">
+        <v>2</v>
+      </c>
+      <c r="K28" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B29">
         <v>4</v>
       </c>
       <c r="C29" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D29" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E29" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F29" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="G29">
         <v>0.5</v>
       </c>
-      <c r="H29">
-        <v>1</v>
-      </c>
-      <c r="M29" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H29" s="2">
+        <v>2</v>
+      </c>
+      <c r="K29" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B30">
         <v>4</v>
       </c>
       <c r="C30" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D30" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E30" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F30" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="G30">
         <v>0.5</v>
       </c>
-      <c r="H30">
-        <v>1</v>
-      </c>
-      <c r="M30" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H30" s="2">
+        <v>2</v>
+      </c>
+      <c r="K30" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B31">
         <v>4</v>
       </c>
       <c r="C31" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D31" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E31" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F31" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G31">
         <v>2</v>
       </c>
-      <c r="H31">
-        <v>4</v>
-      </c>
-      <c r="J31">
-        <v>3</v>
-      </c>
-      <c r="M31" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H31" s="2">
+        <v>2</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="K31" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B32">
         <v>4</v>
       </c>
       <c r="C32" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D32" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E32" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F32" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G32">
         <v>2</v>
       </c>
-      <c r="H32">
-        <v>4</v>
-      </c>
-      <c r="M32" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H32" s="2">
+        <v>2</v>
+      </c>
+      <c r="K32" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B33">
         <v>4</v>
       </c>
       <c r="C33" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D33" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E33" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F33" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G33">
         <v>2</v>
       </c>
-      <c r="H33">
-        <v>4</v>
-      </c>
-      <c r="M33" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H33" s="2">
+        <v>2</v>
+      </c>
+      <c r="K33" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B34">
         <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D34" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E34" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="F34" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="G34">
         <v>0.5</v>
       </c>
-      <c r="H34">
-        <v>1</v>
-      </c>
-      <c r="M34" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H34" s="2">
+        <v>2</v>
+      </c>
+      <c r="K34" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B35">
         <v>5</v>
       </c>
       <c r="C35" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D35" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E35" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F35" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G35">
         <v>0.5</v>
       </c>
-      <c r="H35">
-        <v>1</v>
-      </c>
-      <c r="M35" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H35" s="2">
+        <v>2</v>
+      </c>
+      <c r="K35" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B36">
         <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D36" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G36">
         <v>0.5</v>
       </c>
-      <c r="H36">
-        <v>1</v>
-      </c>
-      <c r="M36" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H36" s="2">
+        <v>2</v>
+      </c>
+      <c r="K36" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B37">
         <v>5</v>
       </c>
       <c r="C37" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D37" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E37" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F37" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="G37">
         <v>0.5</v>
       </c>
-      <c r="H37">
-        <v>1</v>
-      </c>
-      <c r="M37" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H37" s="2">
+        <v>2</v>
+      </c>
+      <c r="K37" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B38">
         <v>5</v>
       </c>
       <c r="C38" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D38" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E38" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F38" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="G38">
         <v>0.5</v>
       </c>
-      <c r="H38">
-        <v>1</v>
-      </c>
-      <c r="M38" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H38" s="2">
+        <v>2</v>
+      </c>
+      <c r="K38" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B39">
         <v>5</v>
       </c>
       <c r="C39" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D39" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E39" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="F39" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="G39">
         <v>0.5</v>
       </c>
-      <c r="H39">
-        <v>1</v>
-      </c>
-      <c r="M39" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H39" s="2">
+        <v>2</v>
+      </c>
+      <c r="K39" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B40">
         <v>5</v>
       </c>
       <c r="C40" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D40" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E40" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F40" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G40">
         <v>0.5</v>
       </c>
-      <c r="H40">
-        <v>1</v>
-      </c>
-      <c r="M40" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H40" s="2">
+        <v>2</v>
+      </c>
+      <c r="K40" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B41">
         <v>5</v>
       </c>
       <c r="C41" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D41" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E41" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F41" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="G41">
         <v>0.5</v>
       </c>
-      <c r="H41">
-        <v>1</v>
-      </c>
-      <c r="M41" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H41" s="2">
+        <v>2</v>
+      </c>
+      <c r="K41" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B42">
         <v>5</v>
       </c>
       <c r="C42" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D42" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E42" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F42" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G42">
         <v>1</v>
       </c>
-      <c r="H42">
-        <v>2</v>
-      </c>
-      <c r="M42" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H42" s="2">
+        <v>2</v>
+      </c>
+      <c r="K42" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B43">
         <v>5</v>
       </c>
       <c r="C43" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D43" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E43" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F43" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G43">
         <v>1</v>
       </c>
-      <c r="H43">
-        <v>2</v>
-      </c>
-      <c r="M43" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H43" s="2">
+        <v>2</v>
+      </c>
+      <c r="K43" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B44">
         <v>6</v>
       </c>
       <c r="C44" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D44" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E44" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="F44" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="G44">
         <v>2</v>
       </c>
-      <c r="H44">
-        <v>4</v>
-      </c>
-      <c r="M44" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H44" s="2">
+        <v>2</v>
+      </c>
+      <c r="K44" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B45">
         <v>6</v>
       </c>
       <c r="C45" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D45" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E45" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F45" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G45">
         <v>2</v>
       </c>
-      <c r="H45">
-        <v>4</v>
-      </c>
-      <c r="M45" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H45" s="2">
+        <v>2</v>
+      </c>
+      <c r="K45" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B46">
         <v>6</v>
       </c>
       <c r="C46" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D46" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E46" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F46" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G46">
         <v>2</v>
       </c>
-      <c r="H46">
-        <v>4</v>
-      </c>
-      <c r="M46" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H46" s="2">
+        <v>2</v>
+      </c>
+      <c r="K46" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B47">
         <v>6</v>
       </c>
       <c r="C47" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D47" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="E47" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F47" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G47">
         <v>2</v>
       </c>
-      <c r="H47">
-        <v>4</v>
-      </c>
-      <c r="M47" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H47" s="2">
+        <v>2</v>
+      </c>
+      <c r="K47" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B48">
         <v>6</v>
       </c>
       <c r="C48" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D48" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E48" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="F48" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="G48">
         <v>2</v>
       </c>
-      <c r="H48">
-        <v>4</v>
-      </c>
-      <c r="M48" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H48" s="2">
+        <v>2</v>
+      </c>
+      <c r="K48" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B49">
         <v>6</v>
       </c>
       <c r="C49" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D49" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E49" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F49" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="G49">
         <v>2</v>
       </c>
-      <c r="H49">
-        <v>4</v>
-      </c>
-      <c r="M49" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H49" s="2">
+        <v>2</v>
+      </c>
+      <c r="K49" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B50">
         <v>6</v>
       </c>
       <c r="C50" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D50" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E50" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F50" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G50">
         <v>2</v>
       </c>
-      <c r="H50">
-        <v>4</v>
-      </c>
-      <c r="M50" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H50" s="2">
+        <v>2</v>
+      </c>
+      <c r="K50" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B51">
         <v>6</v>
       </c>
       <c r="C51" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D51" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="E51" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F51" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="G51">
         <v>2</v>
       </c>
-      <c r="H51">
-        <v>4</v>
-      </c>
-      <c r="M51" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H51" s="2">
+        <v>2</v>
+      </c>
+      <c r="K51" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B52">
         <v>6</v>
       </c>
       <c r="C52" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D52" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="E52" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F52" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G52">
         <v>1</v>
       </c>
-      <c r="H52">
-        <v>2</v>
-      </c>
-      <c r="M52" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H52" s="2">
+        <v>2</v>
+      </c>
+      <c r="K52" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B53">
         <v>6</v>
       </c>
       <c r="C53" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D53" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E53" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F53" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G53">
         <v>1</v>
       </c>
-      <c r="H53">
-        <v>2</v>
-      </c>
-      <c r="M53" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H53" s="2">
+        <v>2</v>
+      </c>
+      <c r="K53" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B54">
         <v>7</v>
       </c>
       <c r="C54" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D54" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E54" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F54" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="G54">
         <v>0.5</v>
       </c>
-      <c r="H54">
-        <v>1</v>
-      </c>
-      <c r="M54" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H54" s="2">
+        <v>2</v>
+      </c>
+      <c r="K54" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B55">
         <v>7</v>
       </c>
       <c r="C55" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D55" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="E55" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="F55" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G55">
         <v>0.5</v>
       </c>
-      <c r="H55">
-        <v>1</v>
-      </c>
-      <c r="M55" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H55" s="2">
+        <v>2</v>
+      </c>
+      <c r="K55" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B56">
         <v>7</v>
       </c>
       <c r="C56" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D56" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E56" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="F56" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G56">
         <v>2</v>
       </c>
-      <c r="H56">
-        <v>4</v>
-      </c>
-      <c r="M56" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H56" s="2">
+        <v>2</v>
+      </c>
+      <c r="K56" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B57">
         <v>7</v>
       </c>
       <c r="C57" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="D57" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="E57" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F57" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G57">
         <v>10</v>
       </c>
-      <c r="H57">
-        <v>20</v>
-      </c>
-      <c r="M57" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H57" s="2">
+        <v>2</v>
+      </c>
+      <c r="K57" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B58">
         <v>7</v>
       </c>
       <c r="C58" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="D58" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E58" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F58" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G58">
         <v>10</v>
       </c>
-      <c r="H58">
-        <v>20</v>
-      </c>
-      <c r="M58" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H58" s="2">
+        <v>2</v>
+      </c>
+      <c r="K58" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B59">
         <v>7</v>
       </c>
       <c r="C59" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D59" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="E59" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F59" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G59">
         <v>2</v>
       </c>
-      <c r="H59">
-        <v>4</v>
-      </c>
-      <c r="M59" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H59" s="2">
+        <v>2</v>
+      </c>
+      <c r="K59" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B60">
         <v>7</v>
       </c>
       <c r="C60" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D60" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E60" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F60" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G60">
         <v>2</v>
       </c>
-      <c r="H60">
-        <v>4</v>
-      </c>
-      <c r="J60">
-        <v>3</v>
-      </c>
-      <c r="M60" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H60" s="2">
+        <v>2</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="K60" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B61">
         <v>7</v>
       </c>
       <c r="C61" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="D61" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="E61" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="F61" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="G61">
         <v>0.25</v>
       </c>
-      <c r="H61">
-        <v>0.5</v>
-      </c>
-      <c r="M61" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H61" s="2">
+        <v>2</v>
+      </c>
+      <c r="K61" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B62">
         <v>8</v>
       </c>
       <c r="C62" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="D62" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E62" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="F62" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G62">
         <v>3</v>
       </c>
-      <c r="H62">
-        <v>6</v>
-      </c>
-      <c r="M62" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H62" s="2">
+        <v>2</v>
+      </c>
+      <c r="K62" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B63">
         <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D63" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E63" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F63" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="G63">
         <v>3</v>
       </c>
-      <c r="H63">
-        <v>6</v>
-      </c>
-      <c r="M63" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H63" s="2">
+        <v>2</v>
+      </c>
+      <c r="K63" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B64">
         <v>8</v>
       </c>
       <c r="C64" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D64" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E64" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F64" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="G64">
         <v>3</v>
       </c>
-      <c r="H64">
-        <v>6</v>
-      </c>
-      <c r="M64" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H64" s="2">
+        <v>2</v>
+      </c>
+      <c r="K64" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B65">
         <v>8</v>
       </c>
       <c r="C65" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="D65" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E65" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F65" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="G65">
         <v>3</v>
       </c>
-      <c r="H65">
-        <v>6</v>
-      </c>
-      <c r="M65" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H65" s="2">
+        <v>2</v>
+      </c>
+      <c r="K65" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B66">
         <v>8</v>
       </c>
       <c r="C66" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="D66" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="E66" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="F66" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="G66">
         <v>3</v>
       </c>
-      <c r="H66">
-        <v>6</v>
-      </c>
-      <c r="M66" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H66" s="2">
+        <v>2</v>
+      </c>
+      <c r="K66" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B67">
         <v>8</v>
       </c>
       <c r="C67" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="D67" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="E67" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F67" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G67">
         <v>3</v>
       </c>
-      <c r="H67">
-        <v>6</v>
-      </c>
-      <c r="M67" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H67" s="2">
+        <v>2</v>
+      </c>
+      <c r="K67" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B68">
         <v>8</v>
       </c>
       <c r="C68" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D68" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="E68" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F68" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="G68">
         <v>3</v>
       </c>
-      <c r="H68">
-        <v>6</v>
-      </c>
-      <c r="M68" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H68" s="2">
+        <v>2</v>
+      </c>
+      <c r="K68" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B69">
         <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D69" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="E69" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F69" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="G69">
         <v>3</v>
       </c>
-      <c r="H69">
-        <v>6</v>
-      </c>
-      <c r="M69" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H69" s="2">
+        <v>2</v>
+      </c>
+      <c r="K69" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B70">
         <v>8</v>
       </c>
       <c r="C70" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="D70" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="E70" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F70" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G70">
         <v>4</v>
       </c>
-      <c r="H70">
-        <v>8</v>
-      </c>
-      <c r="M70" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H70" s="2">
+        <v>2</v>
+      </c>
+      <c r="K70" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B71">
         <v>8</v>
       </c>
       <c r="C71" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D71" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="E71" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F71" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G71">
         <v>5</v>
       </c>
-      <c r="H71">
-        <v>10</v>
-      </c>
-      <c r="M71" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H71" s="2">
+        <v>2</v>
+      </c>
+      <c r="K71" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B72">
         <v>9</v>
       </c>
       <c r="C72" t="s">
+        <v>291</v>
+      </c>
+      <c r="D72" t="s">
+        <v>292</v>
+      </c>
+      <c r="E72" t="s">
+        <v>155</v>
+      </c>
+      <c r="F72" t="s">
+        <v>156</v>
+      </c>
+      <c r="G72">
+        <v>2</v>
+      </c>
+      <c r="H72" s="2">
+        <v>2</v>
+      </c>
+      <c r="K72" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>9</v>
+      </c>
+      <c r="B73">
+        <v>9</v>
+      </c>
+      <c r="C73" t="s">
+        <v>293</v>
+      </c>
+      <c r="D73" t="s">
+        <v>294</v>
+      </c>
+      <c r="E73" t="s">
+        <v>160</v>
+      </c>
+      <c r="F73" t="s">
+        <v>161</v>
+      </c>
+      <c r="G73">
+        <v>2</v>
+      </c>
+      <c r="H73" s="2">
+        <v>2</v>
+      </c>
+      <c r="K73" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>9</v>
+      </c>
+      <c r="B74">
+        <v>9</v>
+      </c>
+      <c r="C74" t="s">
         <v>295</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D74" t="s">
         <v>296</v>
       </c>
-      <c r="E72" t="s">
-        <v>159</v>
-      </c>
-      <c r="F72" t="s">
-        <v>160</v>
-      </c>
-      <c r="G72">
-        <v>2</v>
-      </c>
-      <c r="H72">
-        <v>4</v>
-      </c>
-      <c r="M72" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>13</v>
-      </c>
-      <c r="B73">
-        <v>9</v>
-      </c>
-      <c r="C73" t="s">
+      <c r="E74" t="s">
+        <v>164</v>
+      </c>
+      <c r="F74" t="s">
+        <v>165</v>
+      </c>
+      <c r="G74">
+        <v>2</v>
+      </c>
+      <c r="H74" s="2">
+        <v>2</v>
+      </c>
+      <c r="K74" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>9</v>
+      </c>
+      <c r="B75">
+        <v>9</v>
+      </c>
+      <c r="C75" t="s">
         <v>297</v>
       </c>
-      <c r="D73" t="s">
+      <c r="D75" t="s">
         <v>298</v>
       </c>
-      <c r="E73" t="s">
-        <v>164</v>
-      </c>
-      <c r="F73" t="s">
-        <v>165</v>
-      </c>
-      <c r="G73">
-        <v>2</v>
-      </c>
-      <c r="H73">
-        <v>4</v>
-      </c>
-      <c r="M73" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>13</v>
-      </c>
-      <c r="B74">
-        <v>9</v>
-      </c>
-      <c r="C74" t="s">
+      <c r="E75" t="s">
+        <v>168</v>
+      </c>
+      <c r="F75" t="s">
+        <v>169</v>
+      </c>
+      <c r="G75">
+        <v>2</v>
+      </c>
+      <c r="H75" s="2">
+        <v>2</v>
+      </c>
+      <c r="K75" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>9</v>
+      </c>
+      <c r="B76">
+        <v>9</v>
+      </c>
+      <c r="C76" t="s">
         <v>299</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D76" t="s">
         <v>300</v>
       </c>
-      <c r="E74" t="s">
-        <v>168</v>
-      </c>
-      <c r="F74" t="s">
-        <v>169</v>
-      </c>
-      <c r="G74">
-        <v>2</v>
-      </c>
-      <c r="H74">
-        <v>4</v>
-      </c>
-      <c r="M74" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>13</v>
-      </c>
-      <c r="B75">
-        <v>9</v>
-      </c>
-      <c r="C75" t="s">
+      <c r="E76" t="s">
+        <v>172</v>
+      </c>
+      <c r="F76" t="s">
+        <v>173</v>
+      </c>
+      <c r="G76">
+        <v>2</v>
+      </c>
+      <c r="H76" s="2">
+        <v>2</v>
+      </c>
+      <c r="K76" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>9</v>
+      </c>
+      <c r="B77">
+        <v>9</v>
+      </c>
+      <c r="C77" t="s">
         <v>301</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D77" t="s">
         <v>302</v>
       </c>
-      <c r="E75" t="s">
-        <v>172</v>
-      </c>
-      <c r="F75" t="s">
-        <v>173</v>
-      </c>
-      <c r="G75">
-        <v>2</v>
-      </c>
-      <c r="H75">
-        <v>4</v>
-      </c>
-      <c r="M75" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>13</v>
-      </c>
-      <c r="B76">
-        <v>9</v>
-      </c>
-      <c r="C76" t="s">
+      <c r="E77" t="s">
+        <v>176</v>
+      </c>
+      <c r="F77" t="s">
+        <v>177</v>
+      </c>
+      <c r="G77">
+        <v>2</v>
+      </c>
+      <c r="H77" s="2">
+        <v>2</v>
+      </c>
+      <c r="K77" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>9</v>
+      </c>
+      <c r="B78">
+        <v>9</v>
+      </c>
+      <c r="C78" t="s">
         <v>303</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D78" t="s">
         <v>304</v>
       </c>
-      <c r="E76" t="s">
-        <v>176</v>
-      </c>
-      <c r="F76" t="s">
-        <v>177</v>
-      </c>
-      <c r="G76">
-        <v>2</v>
-      </c>
-      <c r="H76">
-        <v>4</v>
-      </c>
-      <c r="M76" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>13</v>
-      </c>
-      <c r="B77">
-        <v>9</v>
-      </c>
-      <c r="C77" t="s">
+      <c r="E78" t="s">
+        <v>41</v>
+      </c>
+      <c r="F78" t="s">
+        <v>180</v>
+      </c>
+      <c r="G78">
+        <v>2</v>
+      </c>
+      <c r="H78" s="2">
+        <v>2</v>
+      </c>
+      <c r="K78" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>9</v>
+      </c>
+      <c r="B79">
+        <v>9</v>
+      </c>
+      <c r="C79" t="s">
         <v>305</v>
       </c>
-      <c r="D77" t="s">
+      <c r="D79" t="s">
         <v>306</v>
       </c>
-      <c r="E77" t="s">
-        <v>180</v>
-      </c>
-      <c r="F77" t="s">
-        <v>181</v>
-      </c>
-      <c r="G77">
-        <v>2</v>
-      </c>
-      <c r="H77">
-        <v>4</v>
-      </c>
-      <c r="M77" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>13</v>
-      </c>
-      <c r="B78">
-        <v>9</v>
-      </c>
-      <c r="C78" t="s">
+      <c r="E79" t="s">
+        <v>183</v>
+      </c>
+      <c r="F79" t="s">
+        <v>184</v>
+      </c>
+      <c r="G79">
+        <v>2</v>
+      </c>
+      <c r="H79" s="2">
+        <v>2</v>
+      </c>
+      <c r="K79" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>9</v>
+      </c>
+      <c r="B80">
+        <v>9</v>
+      </c>
+      <c r="C80" t="s">
         <v>307</v>
       </c>
-      <c r="D78" t="s">
+      <c r="D80" t="s">
         <v>308</v>
       </c>
-      <c r="E78" t="s">
-        <v>45</v>
-      </c>
-      <c r="F78" t="s">
-        <v>184</v>
-      </c>
-      <c r="G78">
-        <v>2</v>
-      </c>
-      <c r="H78">
-        <v>4</v>
-      </c>
-      <c r="M78" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>13</v>
-      </c>
-      <c r="B79">
-        <v>9</v>
-      </c>
-      <c r="C79" t="s">
+      <c r="E80" t="s">
+        <v>41</v>
+      </c>
+      <c r="F80" t="s">
+        <v>42</v>
+      </c>
+      <c r="G80">
+        <v>2</v>
+      </c>
+      <c r="H80" s="2">
+        <v>2</v>
+      </c>
+      <c r="K80" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>9</v>
+      </c>
+      <c r="B81">
+        <v>9</v>
+      </c>
+      <c r="C81" t="s">
         <v>309</v>
       </c>
-      <c r="D79" t="s">
+      <c r="D81" t="s">
         <v>310</v>
       </c>
-      <c r="E79" t="s">
-        <v>187</v>
-      </c>
-      <c r="F79" t="s">
-        <v>188</v>
-      </c>
-      <c r="G79">
-        <v>2</v>
-      </c>
-      <c r="H79">
-        <v>4</v>
-      </c>
-      <c r="M79" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>13</v>
-      </c>
-      <c r="B80">
-        <v>9</v>
-      </c>
-      <c r="C80" t="s">
-        <v>311</v>
-      </c>
-      <c r="D80" t="s">
-        <v>312</v>
-      </c>
-      <c r="E80" t="s">
-        <v>45</v>
-      </c>
-      <c r="F80" t="s">
+      <c r="E81" t="s">
         <v>46</v>
       </c>
-      <c r="G80">
-        <v>2</v>
-      </c>
-      <c r="H80">
-        <v>4</v>
-      </c>
-      <c r="M80" t="s">
+      <c r="F81" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>13</v>
-      </c>
-      <c r="B81">
-        <v>9</v>
-      </c>
-      <c r="C81" t="s">
-        <v>313</v>
-      </c>
-      <c r="D81" t="s">
-        <v>314</v>
-      </c>
-      <c r="E81" t="s">
-        <v>50</v>
-      </c>
-      <c r="F81" t="s">
-        <v>51</v>
-      </c>
       <c r="G81">
         <v>2</v>
       </c>
-      <c r="H81">
-        <v>4</v>
-      </c>
-      <c r="M81" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H81" s="2">
+        <v>2</v>
+      </c>
+      <c r="K81" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B82">
         <v>10</v>
       </c>
       <c r="C82" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D82" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E82" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F82" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G82">
         <v>0.75</v>
       </c>
-      <c r="H82">
-        <v>1.5</v>
-      </c>
-      <c r="M82" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H82" s="2">
+        <v>2</v>
+      </c>
+      <c r="K82" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B83">
         <v>10</v>
       </c>
       <c r="C83" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="D83" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="E83" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F83" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G83">
         <v>0.75</v>
       </c>
-      <c r="H83">
-        <v>1.5</v>
-      </c>
-      <c r="M83" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H83" s="2">
+        <v>2</v>
+      </c>
+      <c r="K83" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B84">
         <v>10</v>
       </c>
       <c r="C84" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="D84" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E84" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F84" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G84">
         <v>0.75</v>
       </c>
-      <c r="H84">
-        <v>1.5</v>
-      </c>
-      <c r="M84" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H84" s="2">
+        <v>2</v>
+      </c>
+      <c r="K84" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B85">
         <v>10</v>
       </c>
       <c r="C85" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D85" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E85" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F85" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G85">
         <v>0.75</v>
       </c>
-      <c r="H85">
-        <v>1.5</v>
-      </c>
-      <c r="M85" s="1" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H85" s="2">
+        <v>2</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B86">
         <v>10</v>
       </c>
       <c r="C86" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="D86" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="E86" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F86" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G86">
         <v>10</v>
       </c>
-      <c r="H86">
-        <v>20</v>
-      </c>
-      <c r="M86" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H86" s="2">
+        <v>2</v>
+      </c>
+      <c r="K86" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B87">
         <v>10</v>
       </c>
       <c r="C87" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D87" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E87" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="F87" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="G87">
         <v>10</v>
       </c>
-      <c r="H87">
-        <v>20</v>
-      </c>
-      <c r="M87" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H87" s="2">
+        <v>2</v>
+      </c>
+      <c r="K87" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B88">
         <v>10</v>
       </c>
       <c r="C88" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="D88" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="E88" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="F88" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="G88">
         <v>1</v>
       </c>
-      <c r="H88">
-        <v>2</v>
-      </c>
-      <c r="M88" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H88" s="2">
+        <v>2</v>
+      </c>
+      <c r="K88" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B89">
         <v>10</v>
       </c>
       <c r="C89" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="D89" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="E89" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F89" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G89">
         <v>2</v>
       </c>
-      <c r="H89">
-        <v>4</v>
-      </c>
-      <c r="J89">
-        <v>1</v>
-      </c>
-      <c r="M89" t="s">
+      <c r="H89" s="2">
+        <v>2</v>
+      </c>
+      <c r="I89" s="1" t="s">
         <v>335</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="K89" t="s">
+        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Talents.xlsx
+++ b/config/Excel/Talents.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\potential-remove-baseline-20261018\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C41F0896-49EA-4479-9BD4-CD174380C9A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B98A2765-2613-4754-82A2-BAE06E145C78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="322">
   <si>
     <t>類型</t>
   </si>
@@ -347,21 +347,6 @@
     <t>對 BOSS 傷害額外提高</t>
   </si>
   <si>
-    <t>t3_potential</t>
-  </si>
-  <si>
-    <t>潛力啟示</t>
-  </si>
-  <si>
-    <t>🔓</t>
-  </si>
-  <si>
-    <t>potentialUnlock</t>
-  </si>
-  <si>
-    <t>解鎖新類型技能「潛力」三個並給予技能點</t>
-  </si>
-  <si>
     <t>t3_allres</t>
   </si>
   <si>
@@ -473,15 +458,6 @@
     <t>被動類技能效果額外提高</t>
   </si>
   <si>
-    <t>t4_potential</t>
-  </si>
-  <si>
-    <t>潛力覺醒</t>
-  </si>
-  <si>
-    <t>🌠</t>
-  </si>
-  <si>
     <t>t4_normalred</t>
   </si>
   <si>
@@ -779,12 +755,6 @@
     <t>🕳️</t>
   </si>
   <si>
-    <t>t7_potential</t>
-  </si>
-  <si>
-    <t>潛力爆發</t>
-  </si>
-  <si>
     <t>t7_totaldmg</t>
   </si>
   <si>
@@ -1020,15 +990,6 @@
   </si>
   <si>
     <t>總傷害額外增幅</t>
-  </si>
-  <si>
-    <t>t10_potential</t>
-  </si>
-  <si>
-    <t>潛力昇華</t>
-  </si>
-  <si>
-    <t>解鎖新類型技能「潛力」一個並給予技能點</t>
   </si>
   <si>
     <t>體質總值額外提高</t>
@@ -1041,12 +1002,6 @@
   <si>
     <t>威脅值</t>
     <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>TRUE</t>
-  </si>
-  <si>
-    <t>潛力已無解鎖限制，改用威能點，此舊解鎖威能停用</t>
   </si>
 </sst>
 </file>
@@ -2024,7 +1979,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K89"/>
+  <dimension ref="A1:K85"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11.625" bestFit="1" customWidth="1"/>
@@ -2051,10 +2006,10 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>334</v>
+        <v>321</v>
       </c>
       <c r="I1" t="s">
         <v>6</v>
@@ -2179,7 +2134,7 @@
         <v>2</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>332</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -2637,16 +2592,10 @@
         <v>107</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="H21" s="2">
         <v>2</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>336</v>
       </c>
       <c r="K21" t="s">
         <v>108</v>
@@ -2666,10 +2615,10 @@
         <v>110</v>
       </c>
       <c r="E22" t="s">
-        <v>111</v>
+        <v>31</v>
       </c>
       <c r="F22" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="G22">
         <v>0.5</v>
@@ -2678,7 +2627,7 @@
         <v>2</v>
       </c>
       <c r="K22" t="s">
-        <v>113</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -2689,16 +2638,16 @@
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D23" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E23" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F23" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G23">
         <v>0.5</v>
@@ -2707,7 +2656,7 @@
         <v>2</v>
       </c>
       <c r="K23" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -2718,16 +2667,16 @@
         <v>3</v>
       </c>
       <c r="C24" t="s">
+        <v>113</v>
+      </c>
+      <c r="D24" t="s">
+        <v>114</v>
+      </c>
+      <c r="E24" t="s">
+        <v>115</v>
+      </c>
+      <c r="F24" t="s">
         <v>116</v>
-      </c>
-      <c r="D24" t="s">
-        <v>117</v>
-      </c>
-      <c r="E24" t="s">
-        <v>36</v>
-      </c>
-      <c r="F24" t="s">
-        <v>37</v>
       </c>
       <c r="G24">
         <v>0.5</v>
@@ -2736,7 +2685,7 @@
         <v>2</v>
       </c>
       <c r="K24" t="s">
-        <v>38</v>
+        <v>117</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -2744,7 +2693,7 @@
         <v>9</v>
       </c>
       <c r="B25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C25" t="s">
         <v>118</v>
@@ -2753,10 +2702,10 @@
         <v>119</v>
       </c>
       <c r="E25" t="s">
+        <v>91</v>
+      </c>
+      <c r="F25" t="s">
         <v>120</v>
-      </c>
-      <c r="F25" t="s">
-        <v>121</v>
       </c>
       <c r="G25">
         <v>0.5</v>
@@ -2765,7 +2714,7 @@
         <v>2</v>
       </c>
       <c r="K25" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -2776,13 +2725,13 @@
         <v>4</v>
       </c>
       <c r="C26" t="s">
+        <v>122</v>
+      </c>
+      <c r="D26" t="s">
         <v>123</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>124</v>
-      </c>
-      <c r="E26" t="s">
-        <v>91</v>
       </c>
       <c r="F26" t="s">
         <v>125</v>
@@ -2811,10 +2760,10 @@
         <v>128</v>
       </c>
       <c r="E27" t="s">
+        <v>31</v>
+      </c>
+      <c r="F27" t="s">
         <v>129</v>
-      </c>
-      <c r="F27" t="s">
-        <v>130</v>
       </c>
       <c r="G27">
         <v>0.5</v>
@@ -2823,7 +2772,7 @@
         <v>2</v>
       </c>
       <c r="K27" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -2834,13 +2783,13 @@
         <v>4</v>
       </c>
       <c r="C28" t="s">
+        <v>131</v>
+      </c>
+      <c r="D28" t="s">
         <v>132</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>133</v>
-      </c>
-      <c r="E28" t="s">
-        <v>31</v>
       </c>
       <c r="F28" t="s">
         <v>134</v>
@@ -2898,19 +2847,19 @@
         <v>142</v>
       </c>
       <c r="E30" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
       <c r="F30" t="s">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="G30">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H30" s="2">
         <v>2</v>
       </c>
       <c r="K30" t="s">
-        <v>145</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -2921,16 +2870,16 @@
         <v>4</v>
       </c>
       <c r="C31" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D31" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E31" t="s">
-        <v>148</v>
+        <v>86</v>
       </c>
       <c r="F31" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="G31">
         <v>2</v>
@@ -2938,14 +2887,8 @@
       <c r="H31" s="2">
         <v>2</v>
       </c>
-      <c r="I31" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="K31" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -2953,28 +2896,28 @@
         <v>9</v>
       </c>
       <c r="B32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C32" t="s">
+        <v>145</v>
+      </c>
+      <c r="D32" t="s">
+        <v>146</v>
+      </c>
+      <c r="E32" t="s">
+        <v>147</v>
+      </c>
+      <c r="F32" t="s">
+        <v>148</v>
+      </c>
+      <c r="G32">
+        <v>0.5</v>
+      </c>
+      <c r="H32" s="2">
+        <v>2</v>
+      </c>
+      <c r="K32" t="s">
         <v>149</v>
-      </c>
-      <c r="D32" t="s">
-        <v>150</v>
-      </c>
-      <c r="E32" t="s">
-        <v>81</v>
-      </c>
-      <c r="F32" t="s">
-        <v>82</v>
-      </c>
-      <c r="G32">
-        <v>2</v>
-      </c>
-      <c r="H32" s="2">
-        <v>2</v>
-      </c>
-      <c r="K32" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -2982,28 +2925,28 @@
         <v>9</v>
       </c>
       <c r="B33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C33" t="s">
+        <v>150</v>
+      </c>
+      <c r="D33" t="s">
         <v>151</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>152</v>
       </c>
-      <c r="E33" t="s">
-        <v>86</v>
-      </c>
       <c r="F33" t="s">
-        <v>87</v>
+        <v>153</v>
       </c>
       <c r="G33">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="H33" s="2">
         <v>2</v>
       </c>
       <c r="K33" t="s">
-        <v>88</v>
+        <v>149</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -3014,16 +2957,16 @@
         <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D34" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E34" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F34" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G34">
         <v>0.5</v>
@@ -3032,7 +2975,7 @@
         <v>2</v>
       </c>
       <c r="K34" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -3061,7 +3004,7 @@
         <v>2</v>
       </c>
       <c r="K35" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -3090,7 +3033,7 @@
         <v>2</v>
       </c>
       <c r="K36" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -3119,7 +3062,7 @@
         <v>2</v>
       </c>
       <c r="K37" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -3136,10 +3079,10 @@
         <v>171</v>
       </c>
       <c r="E38" t="s">
+        <v>41</v>
+      </c>
+      <c r="F38" t="s">
         <v>172</v>
-      </c>
-      <c r="F38" t="s">
-        <v>173</v>
       </c>
       <c r="G38">
         <v>0.5</v>
@@ -3148,7 +3091,7 @@
         <v>2</v>
       </c>
       <c r="K38" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -3159,16 +3102,16 @@
         <v>5</v>
       </c>
       <c r="C39" t="s">
+        <v>173</v>
+      </c>
+      <c r="D39" t="s">
         <v>174</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>175</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>176</v>
-      </c>
-      <c r="F39" t="s">
-        <v>177</v>
       </c>
       <c r="G39">
         <v>0.5</v>
@@ -3177,7 +3120,7 @@
         <v>2</v>
       </c>
       <c r="K39" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -3188,25 +3131,25 @@
         <v>5</v>
       </c>
       <c r="C40" t="s">
+        <v>177</v>
+      </c>
+      <c r="D40" t="s">
         <v>178</v>
       </c>
-      <c r="D40" t="s">
-        <v>179</v>
-      </c>
       <c r="E40" t="s">
-        <v>41</v>
+        <v>106</v>
       </c>
       <c r="F40" t="s">
-        <v>180</v>
+        <v>107</v>
       </c>
       <c r="G40">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H40" s="2">
         <v>2</v>
       </c>
       <c r="K40" t="s">
-        <v>157</v>
+        <v>108</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -3217,25 +3160,25 @@
         <v>5</v>
       </c>
       <c r="C41" t="s">
+        <v>179</v>
+      </c>
+      <c r="D41" t="s">
+        <v>180</v>
+      </c>
+      <c r="E41" t="s">
         <v>181</v>
       </c>
-      <c r="D41" t="s">
-        <v>182</v>
-      </c>
-      <c r="E41" t="s">
-        <v>183</v>
-      </c>
       <c r="F41" t="s">
-        <v>184</v>
+        <v>116</v>
       </c>
       <c r="G41">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H41" s="2">
         <v>2</v>
       </c>
       <c r="K41" t="s">
-        <v>157</v>
+        <v>117</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -3243,28 +3186,28 @@
         <v>9</v>
       </c>
       <c r="B42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C42" t="s">
+        <v>182</v>
+      </c>
+      <c r="D42" t="s">
+        <v>183</v>
+      </c>
+      <c r="E42" t="s">
+        <v>147</v>
+      </c>
+      <c r="F42" t="s">
+        <v>184</v>
+      </c>
+      <c r="G42">
+        <v>2</v>
+      </c>
+      <c r="H42" s="2">
+        <v>2</v>
+      </c>
+      <c r="K42" t="s">
         <v>185</v>
-      </c>
-      <c r="D42" t="s">
-        <v>186</v>
-      </c>
-      <c r="E42" t="s">
-        <v>111</v>
-      </c>
-      <c r="F42" t="s">
-        <v>112</v>
-      </c>
-      <c r="G42">
-        <v>1</v>
-      </c>
-      <c r="H42" s="2">
-        <v>2</v>
-      </c>
-      <c r="K42" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -3272,28 +3215,28 @@
         <v>9</v>
       </c>
       <c r="B43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C43" t="s">
+        <v>186</v>
+      </c>
+      <c r="D43" t="s">
         <v>187</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
+        <v>152</v>
+      </c>
+      <c r="F43" t="s">
         <v>188</v>
       </c>
-      <c r="E43" t="s">
+      <c r="G43">
+        <v>2</v>
+      </c>
+      <c r="H43" s="2">
+        <v>2</v>
+      </c>
+      <c r="K43" t="s">
         <v>189</v>
-      </c>
-      <c r="F43" t="s">
-        <v>121</v>
-      </c>
-      <c r="G43">
-        <v>1</v>
-      </c>
-      <c r="H43" s="2">
-        <v>2</v>
-      </c>
-      <c r="K43" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -3310,7 +3253,7 @@
         <v>191</v>
       </c>
       <c r="E44" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F44" t="s">
         <v>192</v>
@@ -3368,7 +3311,7 @@
         <v>199</v>
       </c>
       <c r="E46" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F46" t="s">
         <v>200</v>
@@ -3397,7 +3340,7 @@
         <v>203</v>
       </c>
       <c r="E47" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F47" t="s">
         <v>204</v>
@@ -3426,7 +3369,7 @@
         <v>207</v>
       </c>
       <c r="E48" t="s">
-        <v>176</v>
+        <v>41</v>
       </c>
       <c r="F48" t="s">
         <v>208</v>
@@ -3455,7 +3398,7 @@
         <v>211</v>
       </c>
       <c r="E49" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F49" t="s">
         <v>212</v>
@@ -3484,19 +3427,19 @@
         <v>215</v>
       </c>
       <c r="E50" t="s">
-        <v>41</v>
+        <v>101</v>
       </c>
       <c r="F50" t="s">
-        <v>216</v>
+        <v>102</v>
       </c>
       <c r="G50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H50" s="2">
         <v>2</v>
       </c>
       <c r="K50" t="s">
-        <v>217</v>
+        <v>103</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -3507,25 +3450,25 @@
         <v>6</v>
       </c>
       <c r="C51" t="s">
+        <v>216</v>
+      </c>
+      <c r="D51" t="s">
+        <v>217</v>
+      </c>
+      <c r="E51" t="s">
         <v>218</v>
       </c>
-      <c r="D51" t="s">
+      <c r="F51" t="s">
         <v>219</v>
       </c>
-      <c r="E51" t="s">
-        <v>183</v>
-      </c>
-      <c r="F51" t="s">
+      <c r="G51">
+        <v>1</v>
+      </c>
+      <c r="H51" s="2">
+        <v>2</v>
+      </c>
+      <c r="K51" t="s">
         <v>220</v>
-      </c>
-      <c r="G51">
-        <v>2</v>
-      </c>
-      <c r="H51" s="2">
-        <v>2</v>
-      </c>
-      <c r="K51" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -3533,28 +3476,28 @@
         <v>9</v>
       </c>
       <c r="B52">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C52" t="s">
+        <v>221</v>
+      </c>
+      <c r="D52" t="s">
         <v>222</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
+        <v>96</v>
+      </c>
+      <c r="F52" t="s">
         <v>223</v>
       </c>
-      <c r="E52" t="s">
-        <v>101</v>
-      </c>
-      <c r="F52" t="s">
-        <v>102</v>
-      </c>
       <c r="G52">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H52" s="2">
         <v>2</v>
       </c>
       <c r="K52" t="s">
-        <v>103</v>
+        <v>224</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -3562,28 +3505,28 @@
         <v>9</v>
       </c>
       <c r="B53">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C53" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D53" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E53" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F53" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G53">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H53" s="2">
         <v>2</v>
       </c>
       <c r="K53" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -3594,25 +3537,25 @@
         <v>7</v>
       </c>
       <c r="C54" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D54" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E54" t="s">
-        <v>96</v>
+        <v>232</v>
       </c>
       <c r="F54" t="s">
-        <v>231</v>
+        <v>107</v>
       </c>
       <c r="G54">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H54" s="2">
         <v>2</v>
       </c>
       <c r="K54" t="s">
-        <v>232</v>
+        <v>108</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -3629,19 +3572,19 @@
         <v>234</v>
       </c>
       <c r="E55" t="s">
-        <v>235</v>
+        <v>175</v>
       </c>
       <c r="F55" t="s">
-        <v>236</v>
+        <v>62</v>
       </c>
       <c r="G55">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="H55" s="2">
         <v>2</v>
       </c>
       <c r="K55" t="s">
-        <v>237</v>
+        <v>63</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -3652,25 +3595,25 @@
         <v>7</v>
       </c>
       <c r="C56" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D56" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E56" t="s">
-        <v>240</v>
+        <v>51</v>
       </c>
       <c r="F56" t="s">
-        <v>112</v>
+        <v>67</v>
       </c>
       <c r="G56">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H56" s="2">
         <v>2</v>
       </c>
       <c r="K56" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -3681,25 +3624,25 @@
         <v>7</v>
       </c>
       <c r="C57" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D57" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="E57" t="s">
-        <v>183</v>
+        <v>239</v>
       </c>
       <c r="F57" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
       <c r="G57">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H57" s="2">
         <v>2</v>
       </c>
       <c r="K57" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -3710,25 +3653,25 @@
         <v>7</v>
       </c>
       <c r="C58" t="s">
+        <v>240</v>
+      </c>
+      <c r="D58" t="s">
+        <v>241</v>
+      </c>
+      <c r="E58" t="s">
+        <v>242</v>
+      </c>
+      <c r="F58" t="s">
         <v>243</v>
       </c>
-      <c r="D58" t="s">
+      <c r="G58">
+        <v>0.25</v>
+      </c>
+      <c r="H58" s="2">
+        <v>2</v>
+      </c>
+      <c r="K58" t="s">
         <v>244</v>
-      </c>
-      <c r="E58" t="s">
-        <v>51</v>
-      </c>
-      <c r="F58" t="s">
-        <v>67</v>
-      </c>
-      <c r="G58">
-        <v>10</v>
-      </c>
-      <c r="H58" s="2">
-        <v>2</v>
-      </c>
-      <c r="K58" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -3736,7 +3679,7 @@
         <v>9</v>
       </c>
       <c r="B59">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C59" t="s">
         <v>245</v>
@@ -3745,19 +3688,19 @@
         <v>246</v>
       </c>
       <c r="E59" t="s">
+        <v>147</v>
+      </c>
+      <c r="F59" t="s">
         <v>247</v>
       </c>
-      <c r="F59" t="s">
-        <v>121</v>
-      </c>
       <c r="G59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H59" s="2">
         <v>2</v>
       </c>
       <c r="K59" t="s">
-        <v>122</v>
+        <v>248</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -3765,34 +3708,28 @@
         <v>9</v>
       </c>
       <c r="B60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C60" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D60" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E60" t="s">
-        <v>56</v>
+        <v>152</v>
       </c>
       <c r="F60" t="s">
-        <v>107</v>
+        <v>251</v>
       </c>
       <c r="G60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H60" s="2">
         <v>2</v>
       </c>
-      <c r="I60" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="J60" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="K60" t="s">
-        <v>108</v>
+        <v>252</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -3800,28 +3737,28 @@
         <v>9</v>
       </c>
       <c r="B61">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D61" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E61" t="s">
-        <v>252</v>
+        <v>156</v>
       </c>
       <c r="F61" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="G61">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="H61" s="2">
         <v>2</v>
       </c>
       <c r="K61" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -3832,16 +3769,16 @@
         <v>8</v>
       </c>
       <c r="C62" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D62" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E62" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="F62" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="G62">
         <v>3</v>
@@ -3850,7 +3787,7 @@
         <v>2</v>
       </c>
       <c r="K62" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -3861,16 +3798,16 @@
         <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D63" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E63" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F63" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G63">
         <v>3</v>
@@ -3879,7 +3816,7 @@
         <v>2</v>
       </c>
       <c r="K63" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -3890,16 +3827,16 @@
         <v>8</v>
       </c>
       <c r="C64" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D64" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E64" t="s">
         <v>164</v>
       </c>
       <c r="F64" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="G64">
         <v>3</v>
@@ -3908,7 +3845,7 @@
         <v>2</v>
       </c>
       <c r="K64" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -3919,16 +3856,16 @@
         <v>8</v>
       </c>
       <c r="C65" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D65" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E65" t="s">
-        <v>168</v>
+        <v>41</v>
       </c>
       <c r="F65" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="G65">
         <v>3</v>
@@ -3937,7 +3874,7 @@
         <v>2</v>
       </c>
       <c r="K65" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -3948,16 +3885,16 @@
         <v>8</v>
       </c>
       <c r="C66" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D66" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E66" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F66" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G66">
         <v>3</v>
@@ -3966,7 +3903,7 @@
         <v>2</v>
       </c>
       <c r="K66" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -3977,25 +3914,25 @@
         <v>8</v>
       </c>
       <c r="C67" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D67" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E67" t="s">
-        <v>172</v>
+        <v>101</v>
       </c>
       <c r="F67" t="s">
-        <v>277</v>
+        <v>102</v>
       </c>
       <c r="G67">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H67" s="2">
         <v>2</v>
       </c>
       <c r="K67" t="s">
-        <v>278</v>
+        <v>103</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -4012,19 +3949,19 @@
         <v>280</v>
       </c>
       <c r="E68" t="s">
-        <v>41</v>
+        <v>218</v>
       </c>
       <c r="F68" t="s">
-        <v>281</v>
+        <v>219</v>
       </c>
       <c r="G68">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H68" s="2">
         <v>2</v>
       </c>
       <c r="K68" t="s">
-        <v>282</v>
+        <v>220</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -4032,28 +3969,28 @@
         <v>9</v>
       </c>
       <c r="B69">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C69" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D69" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E69" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="F69" t="s">
-        <v>285</v>
+        <v>148</v>
       </c>
       <c r="G69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H69" s="2">
         <v>2</v>
       </c>
       <c r="K69" t="s">
-        <v>286</v>
+        <v>149</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -4061,28 +3998,28 @@
         <v>9</v>
       </c>
       <c r="B70">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C70" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D70" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="E70" t="s">
-        <v>101</v>
+        <v>152</v>
       </c>
       <c r="F70" t="s">
-        <v>102</v>
+        <v>153</v>
       </c>
       <c r="G70">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H70" s="2">
         <v>2</v>
       </c>
       <c r="K70" t="s">
-        <v>103</v>
+        <v>149</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -4090,28 +4027,28 @@
         <v>9</v>
       </c>
       <c r="B71">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C71" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="D71" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E71" t="s">
-        <v>226</v>
+        <v>156</v>
       </c>
       <c r="F71" t="s">
-        <v>227</v>
+        <v>157</v>
       </c>
       <c r="G71">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H71" s="2">
         <v>2</v>
       </c>
       <c r="K71" t="s">
-        <v>228</v>
+        <v>149</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -4122,16 +4059,16 @@
         <v>9</v>
       </c>
       <c r="C72" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="D72" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="E72" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="F72" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="G72">
         <v>2</v>
@@ -4140,7 +4077,7 @@
         <v>2</v>
       </c>
       <c r="K72" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -4151,16 +4088,16 @@
         <v>9</v>
       </c>
       <c r="C73" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D73" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="E73" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F73" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="G73">
         <v>2</v>
@@ -4169,7 +4106,7 @@
         <v>2</v>
       </c>
       <c r="K73" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -4180,16 +4117,16 @@
         <v>9</v>
       </c>
       <c r="C74" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D74" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="E74" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F74" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G74">
         <v>2</v>
@@ -4198,7 +4135,7 @@
         <v>2</v>
       </c>
       <c r="K74" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -4209,16 +4146,16 @@
         <v>9</v>
       </c>
       <c r="C75" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="D75" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="E75" t="s">
-        <v>168</v>
+        <v>41</v>
       </c>
       <c r="F75" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G75">
         <v>2</v>
@@ -4227,7 +4164,7 @@
         <v>2</v>
       </c>
       <c r="K75" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -4238,16 +4175,16 @@
         <v>9</v>
       </c>
       <c r="C76" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="D76" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="E76" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F76" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G76">
         <v>2</v>
@@ -4256,7 +4193,7 @@
         <v>2</v>
       </c>
       <c r="K76" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -4267,16 +4204,16 @@
         <v>9</v>
       </c>
       <c r="C77" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="D77" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="E77" t="s">
-        <v>176</v>
+        <v>41</v>
       </c>
       <c r="F77" t="s">
-        <v>177</v>
+        <v>42</v>
       </c>
       <c r="G77">
         <v>2</v>
@@ -4285,7 +4222,7 @@
         <v>2</v>
       </c>
       <c r="K77" t="s">
-        <v>157</v>
+        <v>43</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -4296,16 +4233,16 @@
         <v>9</v>
       </c>
       <c r="C78" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D78" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="E78" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F78" t="s">
-        <v>180</v>
+        <v>47</v>
       </c>
       <c r="G78">
         <v>2</v>
@@ -4314,7 +4251,7 @@
         <v>2</v>
       </c>
       <c r="K78" t="s">
-        <v>157</v>
+        <v>48</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -4322,28 +4259,28 @@
         <v>9</v>
       </c>
       <c r="B79">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C79" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D79" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="E79" t="s">
-        <v>183</v>
+        <v>12</v>
       </c>
       <c r="F79" t="s">
-        <v>184</v>
+        <v>13</v>
       </c>
       <c r="G79">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="H79" s="2">
         <v>2</v>
       </c>
       <c r="K79" t="s">
-        <v>157</v>
+        <v>14</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -4351,28 +4288,28 @@
         <v>9</v>
       </c>
       <c r="B80">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C80" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="D80" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="E80" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="F80" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="G80">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="H80" s="2">
         <v>2</v>
       </c>
       <c r="K80" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -4380,28 +4317,28 @@
         <v>9</v>
       </c>
       <c r="B81">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C81" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="D81" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="E81" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="F81" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="G81">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="H81" s="2">
         <v>2</v>
       </c>
       <c r="K81" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -4412,16 +4349,16 @@
         <v>10</v>
       </c>
       <c r="C82" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="D82" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E82" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F82" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G82">
         <v>0.75</v>
@@ -4429,8 +4366,8 @@
       <c r="H82" s="2">
         <v>2</v>
       </c>
-      <c r="K82" t="s">
-        <v>14</v>
+      <c r="K82" s="1" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -4441,25 +4378,25 @@
         <v>10</v>
       </c>
       <c r="C83" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D83" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="E83" t="s">
-        <v>17</v>
+        <v>218</v>
       </c>
       <c r="F83" t="s">
-        <v>18</v>
+        <v>219</v>
       </c>
       <c r="G83">
-        <v>0.75</v>
+        <v>10</v>
       </c>
       <c r="H83" s="2">
         <v>2</v>
       </c>
       <c r="K83" t="s">
-        <v>19</v>
+        <v>220</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -4470,25 +4407,25 @@
         <v>10</v>
       </c>
       <c r="C84" t="s">
+        <v>311</v>
+      </c>
+      <c r="D84" t="s">
+        <v>312</v>
+      </c>
+      <c r="E84" t="s">
+        <v>313</v>
+      </c>
+      <c r="F84" t="s">
+        <v>314</v>
+      </c>
+      <c r="G84">
+        <v>10</v>
+      </c>
+      <c r="H84" s="2">
+        <v>2</v>
+      </c>
+      <c r="K84" t="s">
         <v>315</v>
-      </c>
-      <c r="D84" t="s">
-        <v>316</v>
-      </c>
-      <c r="E84" t="s">
-        <v>22</v>
-      </c>
-      <c r="F84" t="s">
-        <v>23</v>
-      </c>
-      <c r="G84">
-        <v>0.75</v>
-      </c>
-      <c r="H84" s="2">
-        <v>2</v>
-      </c>
-      <c r="K84" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
@@ -4499,147 +4436,25 @@
         <v>10</v>
       </c>
       <c r="C85" t="s">
+        <v>316</v>
+      </c>
+      <c r="D85" t="s">
         <v>317</v>
       </c>
-      <c r="D85" t="s">
+      <c r="E85" t="s">
+        <v>242</v>
+      </c>
+      <c r="F85" t="s">
+        <v>243</v>
+      </c>
+      <c r="G85">
+        <v>1</v>
+      </c>
+      <c r="H85" s="2">
+        <v>2</v>
+      </c>
+      <c r="K85" t="s">
         <v>318</v>
-      </c>
-      <c r="E85" t="s">
-        <v>27</v>
-      </c>
-      <c r="F85" t="s">
-        <v>28</v>
-      </c>
-      <c r="G85">
-        <v>0.75</v>
-      </c>
-      <c r="H85" s="2">
-        <v>2</v>
-      </c>
-      <c r="K85" s="1" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>9</v>
-      </c>
-      <c r="B86">
-        <v>10</v>
-      </c>
-      <c r="C86" t="s">
-        <v>319</v>
-      </c>
-      <c r="D86" t="s">
-        <v>320</v>
-      </c>
-      <c r="E86" t="s">
-        <v>226</v>
-      </c>
-      <c r="F86" t="s">
-        <v>227</v>
-      </c>
-      <c r="G86">
-        <v>10</v>
-      </c>
-      <c r="H86" s="2">
-        <v>2</v>
-      </c>
-      <c r="K86" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>9</v>
-      </c>
-      <c r="B87">
-        <v>10</v>
-      </c>
-      <c r="C87" t="s">
-        <v>321</v>
-      </c>
-      <c r="D87" t="s">
-        <v>322</v>
-      </c>
-      <c r="E87" t="s">
-        <v>323</v>
-      </c>
-      <c r="F87" t="s">
-        <v>324</v>
-      </c>
-      <c r="G87">
-        <v>10</v>
-      </c>
-      <c r="H87" s="2">
-        <v>2</v>
-      </c>
-      <c r="K87" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>9</v>
-      </c>
-      <c r="B88">
-        <v>10</v>
-      </c>
-      <c r="C88" t="s">
-        <v>326</v>
-      </c>
-      <c r="D88" t="s">
-        <v>327</v>
-      </c>
-      <c r="E88" t="s">
-        <v>252</v>
-      </c>
-      <c r="F88" t="s">
-        <v>253</v>
-      </c>
-      <c r="G88">
-        <v>1</v>
-      </c>
-      <c r="H88" s="2">
-        <v>2</v>
-      </c>
-      <c r="K88" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>9</v>
-      </c>
-      <c r="B89">
-        <v>10</v>
-      </c>
-      <c r="C89" t="s">
-        <v>329</v>
-      </c>
-      <c r="D89" t="s">
-        <v>330</v>
-      </c>
-      <c r="E89" t="s">
-        <v>46</v>
-      </c>
-      <c r="F89" t="s">
-        <v>107</v>
-      </c>
-      <c r="G89">
-        <v>2</v>
-      </c>
-      <c r="H89" s="2">
-        <v>2</v>
-      </c>
-      <c r="I89" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="J89" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="K89" t="s">
-        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Talents.xlsx
+++ b/config/Excel/Talents.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\potential-remove-baseline-20261018\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B98A2765-2613-4754-82A2-BAE06E145C78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E31F5EDE-3391-49B3-A548-311CB6EAF666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Talents" sheetId="1" r:id="rId1"/>
@@ -779,9 +779,6 @@
     <t>resVsFire</t>
   </si>
   <si>
-    <t>對火屬性敵人抗性提高</t>
-  </si>
-  <si>
     <t>t8_rvsice</t>
   </si>
   <si>
@@ -791,9 +788,6 @@
     <t>resVsIce</t>
   </si>
   <si>
-    <t>對冰屬性敵人抗性提高</t>
-  </si>
-  <si>
     <t>t8_rvslightning</t>
   </si>
   <si>
@@ -803,9 +797,6 @@
     <t>resVsLightning</t>
   </si>
   <si>
-    <t>對電屬性敵人抗性提高</t>
-  </si>
-  <si>
     <t>t8_rvspoison</t>
   </si>
   <si>
@@ -815,9 +806,6 @@
     <t>resVsPoison</t>
   </si>
   <si>
-    <t>對毒屬性敵人抗性提高</t>
-  </si>
-  <si>
     <t>t8_rvsdark</t>
   </si>
   <si>
@@ -827,9 +815,6 @@
     <t>resVsDark</t>
   </si>
   <si>
-    <t>對暗屬性敵人抗性提高</t>
-  </si>
-  <si>
     <t>t8_rvslight</t>
   </si>
   <si>
@@ -839,9 +824,6 @@
     <t>resVsLight</t>
   </si>
   <si>
-    <t>對聖屬性敵人抗性提高</t>
-  </si>
-  <si>
     <t>t8_rvsearth</t>
   </si>
   <si>
@@ -851,9 +833,6 @@
     <t>resVsEarth</t>
   </si>
   <si>
-    <t>對地屬性敵人抗性提高</t>
-  </si>
-  <si>
     <t>t8_rvswind</t>
   </si>
   <si>
@@ -861,9 +840,6 @@
   </si>
   <si>
     <t>resVsWind</t>
-  </si>
-  <si>
-    <t>對風屬性敵人抗性提高</t>
   </si>
   <si>
     <t>t8_boss</t>
@@ -1001,6 +977,38 @@
   </si>
   <si>
     <t>威脅值</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>對火屬性敵人抗性額外提高</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>對冰屬性敵人抗性額外提高</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>對電屬性敵人抗性額外提高</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>對毒屬性敵人抗性額外提高</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>對暗屬性敵人抗性額外提高</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>對聖屬性敵人抗性額外提高</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>對地屬性敵人抗性額外提高</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>對風屬性敵人抗性額外提高</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1008,7 +1016,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1165,6 +1173,14 @@
       <sz val="9"/>
       <name val="新細明體"/>
       <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -1594,7 +1610,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1603,6 +1619,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1979,14 +2001,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K85"/>
+  <dimension ref="A1:N85"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11.625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="31.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2006,10 +2029,10 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="I1" t="s">
         <v>6</v>
@@ -2021,7 +2044,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2041,7 +2064,7 @@
         <v>13</v>
       </c>
       <c r="G2">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H2" s="2">
         <v>2</v>
@@ -2049,8 +2072,19 @@
       <c r="K2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L2">
+        <f>SUM(H2:H85)</f>
+        <v>500</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <f>COUNTIF(B:B,M2)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -2070,7 +2104,7 @@
         <v>18</v>
       </c>
       <c r="G3">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H3" s="2">
         <v>2</v>
@@ -2078,8 +2112,15 @@
       <c r="K3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M3">
+        <v>2</v>
+      </c>
+      <c r="N3">
+        <f t="shared" ref="N3:N11" si="0">COUNTIF(B:B,M3)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2099,7 +2140,7 @@
         <v>23</v>
       </c>
       <c r="G4">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H4" s="2">
         <v>2</v>
@@ -2107,8 +2148,15 @@
       <c r="K4" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M4">
+        <v>3</v>
+      </c>
+      <c r="N4">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -2128,16 +2176,23 @@
         <v>28</v>
       </c>
       <c r="G5">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H5" s="2">
         <v>2</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+        <v>311</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -2157,7 +2212,7 @@
         <v>32</v>
       </c>
       <c r="G6">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H6" s="2">
         <v>2</v>
@@ -2165,8 +2220,15 @@
       <c r="K6" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M6">
+        <v>5</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -2186,7 +2248,7 @@
         <v>37</v>
       </c>
       <c r="G7">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H7" s="2">
         <v>2</v>
@@ -2194,8 +2256,15 @@
       <c r="K7" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M7">
+        <v>6</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -2215,7 +2284,7 @@
         <v>42</v>
       </c>
       <c r="G8">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H8" s="2">
         <v>2</v>
@@ -2223,8 +2292,15 @@
       <c r="K8" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M8">
+        <v>7</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -2244,7 +2320,7 @@
         <v>47</v>
       </c>
       <c r="G9">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H9" s="2">
         <v>2</v>
@@ -2252,8 +2328,15 @@
       <c r="K9" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M9">
+        <v>8</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -2276,13 +2359,20 @@
         <v>5</v>
       </c>
       <c r="H10" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K10" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M10">
+        <v>9</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -2302,16 +2392,23 @@
         <v>57</v>
       </c>
       <c r="G11">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H11" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K11" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M11">
+        <v>10</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -2331,7 +2428,7 @@
         <v>62</v>
       </c>
       <c r="G12">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H12" s="2">
         <v>2</v>
@@ -2340,7 +2437,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -2360,7 +2457,7 @@
         <v>67</v>
       </c>
       <c r="G13">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H13" s="2">
         <v>2</v>
@@ -2369,7 +2466,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -2389,16 +2486,16 @@
         <v>72</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H14" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K14" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>9</v>
       </c>
@@ -2418,16 +2515,16 @@
         <v>77</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H15" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -2447,7 +2544,7 @@
         <v>82</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" s="2">
         <v>2</v>
@@ -2476,7 +2573,7 @@
         <v>87</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" s="2">
         <v>2</v>
@@ -2505,7 +2602,7 @@
         <v>92</v>
       </c>
       <c r="G18">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="H18" s="2">
         <v>2</v>
@@ -2534,7 +2631,7 @@
         <v>97</v>
       </c>
       <c r="G19">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H19" s="2">
         <v>2</v>
@@ -2563,7 +2660,7 @@
         <v>102</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="2">
         <v>2</v>
@@ -2592,10 +2689,10 @@
         <v>107</v>
       </c>
       <c r="G21">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H21" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K21" t="s">
         <v>108</v>
@@ -2621,10 +2718,10 @@
         <v>32</v>
       </c>
       <c r="G22">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="H22" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K22" t="s">
         <v>33</v>
@@ -2650,10 +2747,10 @@
         <v>37</v>
       </c>
       <c r="G23">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="H23" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23" t="s">
         <v>38</v>
@@ -2679,10 +2776,10 @@
         <v>116</v>
       </c>
       <c r="G24">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H24" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K24" t="s">
         <v>117</v>
@@ -2708,12 +2805,12 @@
         <v>120</v>
       </c>
       <c r="G25">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="H25" s="2">
-        <v>2</v>
-      </c>
-      <c r="K25" t="s">
+        <v>3</v>
+      </c>
+      <c r="K25" s="3" t="s">
         <v>121</v>
       </c>
     </row>
@@ -2737,12 +2834,12 @@
         <v>125</v>
       </c>
       <c r="G26">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="H26" s="2">
-        <v>2</v>
-      </c>
-      <c r="K26" t="s">
+        <v>3</v>
+      </c>
+      <c r="K26" s="4" t="s">
         <v>126</v>
       </c>
     </row>
@@ -2766,12 +2863,12 @@
         <v>129</v>
       </c>
       <c r="G27">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="H27" s="2">
-        <v>2</v>
-      </c>
-      <c r="K27" t="s">
+        <v>3</v>
+      </c>
+      <c r="K27" s="4" t="s">
         <v>130</v>
       </c>
     </row>
@@ -2798,9 +2895,9 @@
         <v>0.5</v>
       </c>
       <c r="H28" s="2">
-        <v>2</v>
-      </c>
-      <c r="K28" t="s">
+        <v>3</v>
+      </c>
+      <c r="K28" s="4" t="s">
         <v>135</v>
       </c>
     </row>
@@ -2824,12 +2921,12 @@
         <v>139</v>
       </c>
       <c r="G29">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="H29" s="2">
-        <v>2</v>
-      </c>
-      <c r="K29" t="s">
+        <v>3</v>
+      </c>
+      <c r="K29" s="4" t="s">
         <v>140</v>
       </c>
     </row>
@@ -2856,7 +2953,7 @@
         <v>2</v>
       </c>
       <c r="H30" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K30" t="s">
         <v>83</v>
@@ -2885,7 +2982,7 @@
         <v>2</v>
       </c>
       <c r="H31" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K31" t="s">
         <v>88</v>
@@ -2911,10 +3008,10 @@
         <v>148</v>
       </c>
       <c r="G32">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="H32" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K32" t="s">
         <v>149</v>
@@ -2940,10 +3037,10 @@
         <v>153</v>
       </c>
       <c r="G33">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="H33" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K33" t="s">
         <v>149</v>
@@ -2969,10 +3066,10 @@
         <v>157</v>
       </c>
       <c r="G34">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="H34" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K34" t="s">
         <v>149</v>
@@ -2998,10 +3095,10 @@
         <v>161</v>
       </c>
       <c r="G35">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="H35" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K35" t="s">
         <v>149</v>
@@ -3027,10 +3124,10 @@
         <v>165</v>
       </c>
       <c r="G36">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="H36" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K36" t="s">
         <v>149</v>
@@ -3056,10 +3153,10 @@
         <v>169</v>
       </c>
       <c r="G37">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="H37" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K37" t="s">
         <v>149</v>
@@ -3085,10 +3182,10 @@
         <v>172</v>
       </c>
       <c r="G38">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="H38" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K38" t="s">
         <v>149</v>
@@ -3114,10 +3211,10 @@
         <v>176</v>
       </c>
       <c r="G39">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="H39" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K39" t="s">
         <v>149</v>
@@ -3143,10 +3240,10 @@
         <v>107</v>
       </c>
       <c r="G40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H40" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K40" t="s">
         <v>108</v>
@@ -3172,10 +3269,10 @@
         <v>116</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K41" t="s">
         <v>117</v>
@@ -3201,10 +3298,10 @@
         <v>184</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H42" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K42" t="s">
         <v>185</v>
@@ -3230,10 +3327,10 @@
         <v>188</v>
       </c>
       <c r="G43">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H43" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K43" t="s">
         <v>189</v>
@@ -3259,10 +3356,10 @@
         <v>192</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H44" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K44" t="s">
         <v>193</v>
@@ -3288,10 +3385,10 @@
         <v>196</v>
       </c>
       <c r="G45">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H45" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K45" t="s">
         <v>197</v>
@@ -3317,10 +3414,10 @@
         <v>200</v>
       </c>
       <c r="G46">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H46" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K46" t="s">
         <v>201</v>
@@ -3346,10 +3443,10 @@
         <v>204</v>
       </c>
       <c r="G47">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H47" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K47" t="s">
         <v>205</v>
@@ -3375,10 +3472,10 @@
         <v>208</v>
       </c>
       <c r="G48">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H48" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K48" t="s">
         <v>209</v>
@@ -3404,10 +3501,10 @@
         <v>212</v>
       </c>
       <c r="G49">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H49" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K49" t="s">
         <v>213</v>
@@ -3433,10 +3530,10 @@
         <v>102</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H50" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K50" t="s">
         <v>103</v>
@@ -3462,10 +3559,10 @@
         <v>219</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H51" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K51" t="s">
         <v>220</v>
@@ -3491,10 +3588,10 @@
         <v>223</v>
       </c>
       <c r="G52">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="H52" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K52" t="s">
         <v>224</v>
@@ -3520,10 +3617,10 @@
         <v>228</v>
       </c>
       <c r="G53">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="H53" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K53" t="s">
         <v>229</v>
@@ -3549,10 +3646,10 @@
         <v>107</v>
       </c>
       <c r="G54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H54" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K54" t="s">
         <v>108</v>
@@ -3578,10 +3675,10 @@
         <v>62</v>
       </c>
       <c r="G55">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H55" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K55" t="s">
         <v>63</v>
@@ -3607,10 +3704,10 @@
         <v>67</v>
       </c>
       <c r="G56">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H56" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K56" t="s">
         <v>68</v>
@@ -3636,10 +3733,10 @@
         <v>116</v>
       </c>
       <c r="G57">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H57" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K57" t="s">
         <v>117</v>
@@ -3665,10 +3762,10 @@
         <v>243</v>
       </c>
       <c r="G58">
-        <v>0.25</v>
+        <v>4</v>
       </c>
       <c r="H58" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K58" t="s">
         <v>244</v>
@@ -3694,13 +3791,13 @@
         <v>247</v>
       </c>
       <c r="G59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H59" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K59" t="s">
-        <v>248</v>
+        <v>314</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -3711,25 +3808,25 @@
         <v>8</v>
       </c>
       <c r="C60" t="s">
+        <v>248</v>
+      </c>
+      <c r="D60" t="s">
         <v>249</v>
-      </c>
-      <c r="D60" t="s">
-        <v>250</v>
       </c>
       <c r="E60" t="s">
         <v>152</v>
       </c>
       <c r="F60" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H60" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K60" t="s">
-        <v>252</v>
+        <v>315</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -3740,25 +3837,25 @@
         <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D61" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E61" t="s">
         <v>156</v>
       </c>
       <c r="F61" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H61" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K61" t="s">
-        <v>256</v>
+        <v>316</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -3769,25 +3866,25 @@
         <v>8</v>
       </c>
       <c r="C62" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D62" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="E62" t="s">
         <v>160</v>
       </c>
       <c r="F62" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="G62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H62" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K62" t="s">
-        <v>260</v>
+        <v>317</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -3798,25 +3895,25 @@
         <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D63" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="E63" t="s">
         <v>168</v>
       </c>
       <c r="F63" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="G63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H63" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K63" t="s">
-        <v>264</v>
+        <v>318</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -3827,25 +3924,25 @@
         <v>8</v>
       </c>
       <c r="C64" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="D64" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="E64" t="s">
         <v>164</v>
       </c>
       <c r="F64" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="G64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H64" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K64" t="s">
-        <v>268</v>
+        <v>319</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -3856,25 +3953,25 @@
         <v>8</v>
       </c>
       <c r="C65" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D65" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="E65" t="s">
         <v>41</v>
       </c>
       <c r="F65" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="G65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H65" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K65" t="s">
-        <v>272</v>
+        <v>320</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -3885,25 +3982,25 @@
         <v>8</v>
       </c>
       <c r="C66" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="D66" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="E66" t="s">
         <v>175</v>
       </c>
       <c r="F66" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="G66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H66" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K66" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -3914,10 +4011,10 @@
         <v>8</v>
       </c>
       <c r="C67" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="D67" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="E67" t="s">
         <v>101</v>
@@ -3929,7 +4026,7 @@
         <v>4</v>
       </c>
       <c r="H67" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K67" t="s">
         <v>103</v>
@@ -3943,10 +4040,10 @@
         <v>8</v>
       </c>
       <c r="C68" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="D68" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="E68" t="s">
         <v>218</v>
@@ -3955,10 +4052,10 @@
         <v>219</v>
       </c>
       <c r="G68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H68" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K68" t="s">
         <v>220</v>
@@ -3972,10 +4069,10 @@
         <v>9</v>
       </c>
       <c r="C69" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="D69" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="E69" t="s">
         <v>147</v>
@@ -3984,10 +4081,10 @@
         <v>148</v>
       </c>
       <c r="G69">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H69" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K69" t="s">
         <v>149</v>
@@ -4001,10 +4098,10 @@
         <v>9</v>
       </c>
       <c r="C70" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="D70" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="E70" t="s">
         <v>152</v>
@@ -4013,10 +4110,10 @@
         <v>153</v>
       </c>
       <c r="G70">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H70" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K70" t="s">
         <v>149</v>
@@ -4030,10 +4127,10 @@
         <v>9</v>
       </c>
       <c r="C71" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="D71" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="E71" t="s">
         <v>156</v>
@@ -4042,10 +4139,10 @@
         <v>157</v>
       </c>
       <c r="G71">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H71" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K71" t="s">
         <v>149</v>
@@ -4059,10 +4156,10 @@
         <v>9</v>
       </c>
       <c r="C72" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="D72" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="E72" t="s">
         <v>160</v>
@@ -4071,10 +4168,10 @@
         <v>161</v>
       </c>
       <c r="G72">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H72" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K72" t="s">
         <v>149</v>
@@ -4088,10 +4185,10 @@
         <v>9</v>
       </c>
       <c r="C73" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="D73" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="E73" t="s">
         <v>164</v>
@@ -4100,10 +4197,10 @@
         <v>165</v>
       </c>
       <c r="G73">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H73" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K73" t="s">
         <v>149</v>
@@ -4117,10 +4214,10 @@
         <v>9</v>
       </c>
       <c r="C74" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="D74" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="E74" t="s">
         <v>168</v>
@@ -4129,10 +4226,10 @@
         <v>169</v>
       </c>
       <c r="G74">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H74" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K74" t="s">
         <v>149</v>
@@ -4146,10 +4243,10 @@
         <v>9</v>
       </c>
       <c r="C75" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="D75" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="E75" t="s">
         <v>41</v>
@@ -4158,10 +4255,10 @@
         <v>172</v>
       </c>
       <c r="G75">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H75" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K75" t="s">
         <v>149</v>
@@ -4175,10 +4272,10 @@
         <v>9</v>
       </c>
       <c r="C76" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="D76" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="E76" t="s">
         <v>175</v>
@@ -4187,10 +4284,10 @@
         <v>176</v>
       </c>
       <c r="G76">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H76" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K76" t="s">
         <v>149</v>
@@ -4204,10 +4301,10 @@
         <v>9</v>
       </c>
       <c r="C77" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="D77" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="E77" t="s">
         <v>41</v>
@@ -4216,10 +4313,10 @@
         <v>42</v>
       </c>
       <c r="G77">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H77" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K77" t="s">
         <v>43</v>
@@ -4233,10 +4330,10 @@
         <v>9</v>
       </c>
       <c r="C78" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="D78" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="E78" t="s">
         <v>46</v>
@@ -4245,10 +4342,10 @@
         <v>47</v>
       </c>
       <c r="G78">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H78" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K78" t="s">
         <v>48</v>
@@ -4262,10 +4359,10 @@
         <v>10</v>
       </c>
       <c r="C79" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="D79" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="E79" t="s">
         <v>12</v>
@@ -4274,10 +4371,10 @@
         <v>13</v>
       </c>
       <c r="G79">
-        <v>0.75</v>
+        <v>5</v>
       </c>
       <c r="H79" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K79" t="s">
         <v>14</v>
@@ -4291,10 +4388,10 @@
         <v>10</v>
       </c>
       <c r="C80" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D80" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="E80" t="s">
         <v>17</v>
@@ -4303,10 +4400,10 @@
         <v>18</v>
       </c>
       <c r="G80">
-        <v>0.75</v>
+        <v>5</v>
       </c>
       <c r="H80" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K80" t="s">
         <v>19</v>
@@ -4320,10 +4417,10 @@
         <v>10</v>
       </c>
       <c r="C81" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="D81" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="E81" t="s">
         <v>22</v>
@@ -4332,10 +4429,10 @@
         <v>23</v>
       </c>
       <c r="G81">
-        <v>0.75</v>
+        <v>5</v>
       </c>
       <c r="H81" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K81" t="s">
         <v>24</v>
@@ -4349,10 +4446,10 @@
         <v>10</v>
       </c>
       <c r="C82" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="D82" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="E82" t="s">
         <v>27</v>
@@ -4361,13 +4458,13 @@
         <v>28</v>
       </c>
       <c r="G82">
-        <v>0.75</v>
+        <v>5</v>
       </c>
       <c r="H82" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -4378,10 +4475,10 @@
         <v>10</v>
       </c>
       <c r="C83" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="D83" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="E83" t="s">
         <v>218</v>
@@ -4390,10 +4487,10 @@
         <v>219</v>
       </c>
       <c r="G83">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H83" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K83" t="s">
         <v>220</v>
@@ -4407,25 +4504,25 @@
         <v>10</v>
       </c>
       <c r="C84" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="D84" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="E84" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="F84" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="G84">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H84" s="2">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="K84" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
@@ -4436,10 +4533,10 @@
         <v>10</v>
       </c>
       <c r="C85" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="D85" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="E85" t="s">
         <v>242</v>
@@ -4448,17 +4545,18 @@
         <v>243</v>
       </c>
       <c r="G85">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H85" s="2">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="K85" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/config/Excel/Talents.xlsx
+++ b/config/Excel/Talents.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E31F5EDE-3391-49B3-A548-311CB6EAF666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B874DA1A-EDF3-40CC-8437-4304309709E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Talents" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="335">
   <si>
     <t>類型</t>
   </si>
@@ -1010,6 +1010,45 @@
   <si>
     <t>對風屬性敵人抗性額外提高</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>升級金幣基數</t>
+  </si>
+  <si>
+    <t>升級金幣倍率</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>400000</t>
+  </si>
+  <si>
+    <t>1500000</t>
+  </si>
+  <si>
+    <t>6000000</t>
+  </si>
+  <si>
+    <t>25000000</t>
+  </si>
+  <si>
+    <t>100000000</t>
+  </si>
+  <si>
+    <t>400000000</t>
+  </si>
+  <si>
+    <t>1500000000</t>
+  </si>
+  <si>
+    <t>6000000000</t>
+  </si>
+  <si>
+    <t>25000000000</t>
   </si>
 </sst>
 </file>
@@ -1610,7 +1649,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1624,6 +1663,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2001,15 +2046,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N85"/>
+  <dimension ref="A1:P85"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11.625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="31.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="31.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2040,11 +2086,17 @@
       <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="M1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2069,22 +2121,28 @@
       <c r="H2" s="2">
         <v>2</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M2" t="s">
         <v>14</v>
       </c>
-      <c r="L2">
+      <c r="N2">
         <f>SUM(H2:H85)</f>
         <v>500</v>
       </c>
-      <c r="M2">
+      <c r="O2">
         <v>1</v>
       </c>
-      <c r="N2">
-        <f>COUNTIF(B:B,M2)</f>
+      <c r="P2">
+        <f>COUNTIF(B:B,O2)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -2109,18 +2167,24 @@
       <c r="H3" s="2">
         <v>2</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M3" t="s">
         <v>19</v>
       </c>
-      <c r="M3">
+      <c r="O3">
         <v>2</v>
       </c>
-      <c r="N3">
-        <f t="shared" ref="N3:N11" si="0">COUNTIF(B:B,M3)</f>
+      <c r="P3">
+        <f t="shared" ref="P3:P11" si="0">COUNTIF(B:B,O3)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2145,18 +2209,24 @@
       <c r="H4" s="2">
         <v>2</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M4" t="s">
         <v>24</v>
       </c>
-      <c r="M4">
+      <c r="O4">
         <v>3</v>
       </c>
-      <c r="N4">
+      <c r="P4">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -2182,17 +2252,23 @@
         <v>2</v>
       </c>
       <c r="K5" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M5" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="M5">
-        <v>4</v>
-      </c>
-      <c r="N5">
+      <c r="O5">
+        <v>4</v>
+      </c>
+      <c r="P5">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -2217,18 +2293,24 @@
       <c r="H6" s="2">
         <v>2</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M6" t="s">
         <v>33</v>
       </c>
-      <c r="M6">
+      <c r="O6">
         <v>5</v>
       </c>
-      <c r="N6">
+      <c r="P6">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -2253,18 +2335,24 @@
       <c r="H7" s="2">
         <v>2</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K7" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M7" t="s">
         <v>38</v>
       </c>
-      <c r="M7">
+      <c r="O7">
         <v>6</v>
       </c>
-      <c r="N7">
+      <c r="P7">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -2289,18 +2377,24 @@
       <c r="H8" s="2">
         <v>2</v>
       </c>
-      <c r="K8" t="s">
+      <c r="K8" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M8" t="s">
         <v>43</v>
       </c>
-      <c r="M8">
+      <c r="O8">
         <v>7</v>
       </c>
-      <c r="N8">
+      <c r="P8">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -2325,18 +2419,24 @@
       <c r="H9" s="2">
         <v>2</v>
       </c>
-      <c r="K9" t="s">
+      <c r="K9" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M9" t="s">
         <v>48</v>
       </c>
-      <c r="M9">
+      <c r="O9">
         <v>8</v>
       </c>
-      <c r="N9">
+      <c r="P9">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -2361,18 +2461,24 @@
       <c r="H10" s="2">
         <v>3</v>
       </c>
-      <c r="K10" t="s">
+      <c r="K10" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M10" t="s">
         <v>53</v>
       </c>
-      <c r="M10">
-        <v>9</v>
-      </c>
-      <c r="N10">
+      <c r="O10">
+        <v>9</v>
+      </c>
+      <c r="P10">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -2397,18 +2503,24 @@
       <c r="H11" s="2">
         <v>4</v>
       </c>
-      <c r="K11" t="s">
+      <c r="K11" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M11" t="s">
         <v>58</v>
       </c>
-      <c r="M11">
+      <c r="O11">
         <v>10</v>
       </c>
-      <c r="N11">
+      <c r="P11">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -2433,11 +2545,17 @@
       <c r="H12" s="2">
         <v>2</v>
       </c>
-      <c r="K12" t="s">
+      <c r="K12" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M12" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -2462,11 +2580,17 @@
       <c r="H13" s="2">
         <v>2</v>
       </c>
-      <c r="K13" t="s">
+      <c r="K13" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M13" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -2491,11 +2615,17 @@
       <c r="H14" s="2">
         <v>3</v>
       </c>
-      <c r="K14" t="s">
+      <c r="K14" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M14" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>9</v>
       </c>
@@ -2520,11 +2650,17 @@
       <c r="H15" s="2">
         <v>3</v>
       </c>
-      <c r="K15" t="s">
+      <c r="K15" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M15" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -2549,11 +2685,17 @@
       <c r="H16" s="2">
         <v>2</v>
       </c>
-      <c r="K16" t="s">
+      <c r="K16" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M16" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -2578,11 +2720,17 @@
       <c r="H17" s="2">
         <v>2</v>
       </c>
-      <c r="K17" t="s">
+      <c r="K17" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M17" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -2607,11 +2755,17 @@
       <c r="H18" s="2">
         <v>2</v>
       </c>
-      <c r="K18" t="s">
+      <c r="K18" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M18" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>9</v>
       </c>
@@ -2636,11 +2790,17 @@
       <c r="H19" s="2">
         <v>2</v>
       </c>
-      <c r="K19" t="s">
+      <c r="K19" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M19" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -2665,11 +2825,17 @@
       <c r="H20" s="2">
         <v>2</v>
       </c>
-      <c r="K20" t="s">
+      <c r="K20" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M20" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -2694,11 +2860,17 @@
       <c r="H21" s="2">
         <v>3</v>
       </c>
-      <c r="K21" t="s">
+      <c r="K21" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M21" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>9</v>
       </c>
@@ -2723,11 +2895,17 @@
       <c r="H22" s="2">
         <v>3</v>
       </c>
-      <c r="K22" t="s">
+      <c r="K22" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M22" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>9</v>
       </c>
@@ -2752,11 +2930,17 @@
       <c r="H23" s="2">
         <v>3</v>
       </c>
-      <c r="K23" t="s">
+      <c r="K23" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M23" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -2781,11 +2965,17 @@
       <c r="H24" s="2">
         <v>3</v>
       </c>
-      <c r="K24" t="s">
+      <c r="K24" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M24" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>9</v>
       </c>
@@ -2810,11 +3000,17 @@
       <c r="H25" s="2">
         <v>3</v>
       </c>
-      <c r="K25" s="3" t="s">
+      <c r="K25" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="M25" s="3" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>9</v>
       </c>
@@ -2839,11 +3035,17 @@
       <c r="H26" s="2">
         <v>3</v>
       </c>
-      <c r="K26" s="4" t="s">
+      <c r="K26" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="M26" s="4" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -2868,11 +3070,17 @@
       <c r="H27" s="2">
         <v>3</v>
       </c>
-      <c r="K27" s="4" t="s">
+      <c r="K27" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="M27" s="4" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>9</v>
       </c>
@@ -2897,11 +3105,17 @@
       <c r="H28" s="2">
         <v>3</v>
       </c>
-      <c r="K28" s="4" t="s">
+      <c r="K28" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="M28" s="4" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>9</v>
       </c>
@@ -2926,11 +3140,17 @@
       <c r="H29" s="2">
         <v>3</v>
       </c>
-      <c r="K29" s="4" t="s">
+      <c r="K29" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="L29" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="M29" s="4" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>9</v>
       </c>
@@ -2955,11 +3175,17 @@
       <c r="H30" s="2">
         <v>3</v>
       </c>
-      <c r="K30" t="s">
+      <c r="K30" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M30" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>9</v>
       </c>
@@ -2984,11 +3210,17 @@
       <c r="H31" s="2">
         <v>3</v>
       </c>
-      <c r="K31" t="s">
+      <c r="K31" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M31" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>9</v>
       </c>
@@ -3013,11 +3245,17 @@
       <c r="H32" s="2">
         <v>4</v>
       </c>
-      <c r="K32" t="s">
+      <c r="K32" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M32" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>9</v>
       </c>
@@ -3042,11 +3280,17 @@
       <c r="H33" s="2">
         <v>4</v>
       </c>
-      <c r="K33" t="s">
+      <c r="K33" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M33" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>9</v>
       </c>
@@ -3071,11 +3315,17 @@
       <c r="H34" s="2">
         <v>4</v>
       </c>
-      <c r="K34" t="s">
+      <c r="K34" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M34" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>9</v>
       </c>
@@ -3100,11 +3350,17 @@
       <c r="H35" s="2">
         <v>4</v>
       </c>
-      <c r="K35" t="s">
+      <c r="K35" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M35" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>9</v>
       </c>
@@ -3129,11 +3385,17 @@
       <c r="H36" s="2">
         <v>4</v>
       </c>
-      <c r="K36" t="s">
+      <c r="K36" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M36" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>9</v>
       </c>
@@ -3158,11 +3420,17 @@
       <c r="H37" s="2">
         <v>4</v>
       </c>
-      <c r="K37" t="s">
+      <c r="K37" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M37" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>9</v>
       </c>
@@ -3187,11 +3455,17 @@
       <c r="H38" s="2">
         <v>4</v>
       </c>
-      <c r="K38" t="s">
+      <c r="K38" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M38" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>9</v>
       </c>
@@ -3216,11 +3490,17 @@
       <c r="H39" s="2">
         <v>4</v>
       </c>
-      <c r="K39" t="s">
+      <c r="K39" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M39" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>9</v>
       </c>
@@ -3245,11 +3525,17 @@
       <c r="H40" s="2">
         <v>4</v>
       </c>
-      <c r="K40" t="s">
+      <c r="K40" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M40" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>9</v>
       </c>
@@ -3274,11 +3560,17 @@
       <c r="H41" s="2">
         <v>4</v>
       </c>
-      <c r="K41" t="s">
+      <c r="K41" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M41" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>9</v>
       </c>
@@ -3303,11 +3595,17 @@
       <c r="H42" s="2">
         <v>4</v>
       </c>
-      <c r="K42" t="s">
+      <c r="K42" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M42" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -3332,11 +3630,17 @@
       <c r="H43" s="2">
         <v>4</v>
       </c>
-      <c r="K43" t="s">
+      <c r="K43" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M43" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>9</v>
       </c>
@@ -3361,11 +3665,17 @@
       <c r="H44" s="2">
         <v>4</v>
       </c>
-      <c r="K44" t="s">
+      <c r="K44" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M44" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>9</v>
       </c>
@@ -3390,11 +3700,17 @@
       <c r="H45" s="2">
         <v>4</v>
       </c>
-      <c r="K45" t="s">
+      <c r="K45" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M45" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>9</v>
       </c>
@@ -3419,11 +3735,17 @@
       <c r="H46" s="2">
         <v>4</v>
       </c>
-      <c r="K46" t="s">
+      <c r="K46" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M46" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>9</v>
       </c>
@@ -3448,11 +3770,17 @@
       <c r="H47" s="2">
         <v>4</v>
       </c>
-      <c r="K47" t="s">
+      <c r="K47" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M47" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>9</v>
       </c>
@@ -3477,11 +3805,17 @@
       <c r="H48" s="2">
         <v>4</v>
       </c>
-      <c r="K48" t="s">
+      <c r="K48" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M48" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>9</v>
       </c>
@@ -3506,11 +3840,17 @@
       <c r="H49" s="2">
         <v>4</v>
       </c>
-      <c r="K49" t="s">
+      <c r="K49" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M49" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>9</v>
       </c>
@@ -3535,11 +3875,17 @@
       <c r="H50" s="2">
         <v>6</v>
       </c>
-      <c r="K50" t="s">
+      <c r="K50" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M50" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>9</v>
       </c>
@@ -3564,11 +3910,17 @@
       <c r="H51" s="2">
         <v>5</v>
       </c>
-      <c r="K51" t="s">
+      <c r="K51" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M51" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>9</v>
       </c>
@@ -3593,11 +3945,17 @@
       <c r="H52" s="2">
         <v>8</v>
       </c>
-      <c r="K52" t="s">
+      <c r="K52" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M52" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>9</v>
       </c>
@@ -3622,11 +3980,17 @@
       <c r="H53" s="2">
         <v>8</v>
       </c>
-      <c r="K53" t="s">
+      <c r="K53" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M53" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>9</v>
       </c>
@@ -3651,11 +4015,17 @@
       <c r="H54" s="2">
         <v>4</v>
       </c>
-      <c r="K54" t="s">
+      <c r="K54" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M54" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>9</v>
       </c>
@@ -3680,11 +4050,17 @@
       <c r="H55" s="2">
         <v>4</v>
       </c>
-      <c r="K55" t="s">
+      <c r="K55" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M55" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>9</v>
       </c>
@@ -3709,11 +4085,17 @@
       <c r="H56" s="2">
         <v>4</v>
       </c>
-      <c r="K56" t="s">
+      <c r="K56" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M56" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>9</v>
       </c>
@@ -3738,11 +4120,17 @@
       <c r="H57" s="2">
         <v>5</v>
       </c>
-      <c r="K57" t="s">
+      <c r="K57" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M57" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>9</v>
       </c>
@@ -3767,11 +4155,17 @@
       <c r="H58" s="2">
         <v>8</v>
       </c>
-      <c r="K58" t="s">
+      <c r="K58" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M58" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>9</v>
       </c>
@@ -3796,11 +4190,17 @@
       <c r="H59" s="2">
         <v>7</v>
       </c>
-      <c r="K59" t="s">
+      <c r="K59" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M59" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>9</v>
       </c>
@@ -3825,11 +4225,17 @@
       <c r="H60" s="2">
         <v>7</v>
       </c>
-      <c r="K60" t="s">
+      <c r="K60" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M60" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>9</v>
       </c>
@@ -3854,11 +4260,17 @@
       <c r="H61" s="2">
         <v>7</v>
       </c>
-      <c r="K61" t="s">
+      <c r="K61" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="L61" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M61" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>9</v>
       </c>
@@ -3883,11 +4295,17 @@
       <c r="H62" s="2">
         <v>7</v>
       </c>
-      <c r="K62" t="s">
+      <c r="K62" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="L62" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M62" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>9</v>
       </c>
@@ -3912,11 +4330,17 @@
       <c r="H63" s="2">
         <v>7</v>
       </c>
-      <c r="K63" t="s">
+      <c r="K63" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="L63" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M63" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>9</v>
       </c>
@@ -3941,11 +4365,17 @@
       <c r="H64" s="2">
         <v>7</v>
       </c>
-      <c r="K64" t="s">
+      <c r="K64" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M64" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>9</v>
       </c>
@@ -3970,11 +4400,17 @@
       <c r="H65" s="2">
         <v>7</v>
       </c>
-      <c r="K65" t="s">
+      <c r="K65" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="L65" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M65" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>9</v>
       </c>
@@ -3999,11 +4435,17 @@
       <c r="H66" s="2">
         <v>7</v>
       </c>
-      <c r="K66" t="s">
+      <c r="K66" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M66" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>9</v>
       </c>
@@ -4028,11 +4470,17 @@
       <c r="H67" s="2">
         <v>10</v>
       </c>
-      <c r="K67" t="s">
+      <c r="K67" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="L67" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M67" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>9</v>
       </c>
@@ -4057,11 +4505,17 @@
       <c r="H68" s="2">
         <v>10</v>
       </c>
-      <c r="K68" t="s">
+      <c r="K68" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M68" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>9</v>
       </c>
@@ -4086,11 +4540,17 @@
       <c r="H69" s="2">
         <v>10</v>
       </c>
-      <c r="K69" t="s">
+      <c r="K69" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="L69" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M69" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>9</v>
       </c>
@@ -4115,11 +4575,17 @@
       <c r="H70" s="2">
         <v>10</v>
       </c>
-      <c r="K70" t="s">
+      <c r="K70" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="L70" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M70" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>9</v>
       </c>
@@ -4144,11 +4610,17 @@
       <c r="H71" s="2">
         <v>10</v>
       </c>
-      <c r="K71" t="s">
+      <c r="K71" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="L71" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M71" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>9</v>
       </c>
@@ -4173,11 +4645,17 @@
       <c r="H72" s="2">
         <v>10</v>
       </c>
-      <c r="K72" t="s">
+      <c r="K72" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="L72" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M72" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>9</v>
       </c>
@@ -4202,11 +4680,17 @@
       <c r="H73" s="2">
         <v>10</v>
       </c>
-      <c r="K73" t="s">
+      <c r="K73" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="L73" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M73" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>9</v>
       </c>
@@ -4231,11 +4715,17 @@
       <c r="H74" s="2">
         <v>10</v>
       </c>
-      <c r="K74" t="s">
+      <c r="K74" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="L74" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M74" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>9</v>
       </c>
@@ -4260,11 +4750,17 @@
       <c r="H75" s="2">
         <v>10</v>
       </c>
-      <c r="K75" t="s">
+      <c r="K75" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="L75" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M75" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>9</v>
       </c>
@@ -4289,11 +4785,17 @@
       <c r="H76" s="2">
         <v>10</v>
       </c>
-      <c r="K76" t="s">
+      <c r="K76" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="L76" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M76" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>9</v>
       </c>
@@ -4318,11 +4820,17 @@
       <c r="H77" s="2">
         <v>12</v>
       </c>
-      <c r="K77" t="s">
+      <c r="K77" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="L77" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M77" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>9</v>
       </c>
@@ -4347,11 +4855,17 @@
       <c r="H78" s="2">
         <v>12</v>
       </c>
-      <c r="K78" t="s">
+      <c r="K78" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="L78" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M78" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>9</v>
       </c>
@@ -4376,11 +4890,17 @@
       <c r="H79" s="2">
         <v>12</v>
       </c>
-      <c r="K79" t="s">
+      <c r="K79" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="L79" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M79" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>9</v>
       </c>
@@ -4405,11 +4925,17 @@
       <c r="H80" s="2">
         <v>12</v>
       </c>
-      <c r="K80" t="s">
+      <c r="K80" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="L80" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M80" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>9</v>
       </c>
@@ -4434,11 +4960,17 @@
       <c r="H81" s="2">
         <v>12</v>
       </c>
-      <c r="K81" t="s">
+      <c r="K81" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="L81" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M81" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>9</v>
       </c>
@@ -4464,10 +4996,16 @@
         <v>12</v>
       </c>
       <c r="K82" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="L82" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M82" s="1" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>9</v>
       </c>
@@ -4492,11 +5030,17 @@
       <c r="H83" s="2">
         <v>12</v>
       </c>
-      <c r="K83" t="s">
+      <c r="K83" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="L83" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M83" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>9</v>
       </c>
@@ -4521,11 +5065,17 @@
       <c r="H84" s="2">
         <v>25</v>
       </c>
-      <c r="K84" t="s">
+      <c r="K84" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="L84" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M84" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>9</v>
       </c>
@@ -4550,7 +5100,13 @@
       <c r="H85" s="2">
         <v>35</v>
       </c>
-      <c r="K85" t="s">
+      <c r="K85" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="L85" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M85" t="s">
         <v>310</v>
       </c>
     </row>
